--- a/data/corpus.xlsx
+++ b/data/corpus.xlsx
@@ -190,618 +190,618 @@
     <t>letter00021</t>
   </si>
   <si>
+    <t>letter00029</t>
+  </si>
+  <si>
+    <t>letter00033</t>
+  </si>
+  <si>
+    <t>letter00035</t>
+  </si>
+  <si>
+    <t>letter00037</t>
+  </si>
+  <si>
+    <t>letter00039</t>
+  </si>
+  <si>
+    <t>letter00041</t>
+  </si>
+  <si>
+    <t>letter00043</t>
+  </si>
+  <si>
+    <t>letter00045</t>
+  </si>
+  <si>
+    <t>letter00047</t>
+  </si>
+  <si>
+    <t>letter00049</t>
+  </si>
+  <si>
+    <t>letter00051</t>
+  </si>
+  <si>
+    <t>letter00053</t>
+  </si>
+  <si>
+    <t>letter00057</t>
+  </si>
+  <si>
+    <t>letter00059</t>
+  </si>
+  <si>
+    <t>letter00065</t>
+  </si>
+  <si>
+    <t>letter00067</t>
+  </si>
+  <si>
+    <t>letter00069</t>
+  </si>
+  <si>
+    <t>letter00071</t>
+  </si>
+  <si>
+    <t>letter00073</t>
+  </si>
+  <si>
+    <t>letter00075</t>
+  </si>
+  <si>
+    <t>letter00077</t>
+  </si>
+  <si>
+    <t>letter00079</t>
+  </si>
+  <si>
+    <t>letter00080</t>
+  </si>
+  <si>
+    <t>letter00082</t>
+  </si>
+  <si>
+    <t>letter00084</t>
+  </si>
+  <si>
+    <t>letter00086</t>
+  </si>
+  <si>
+    <t>letter00088</t>
+  </si>
+  <si>
+    <t>letter00090</t>
+  </si>
+  <si>
+    <t>letter00092</t>
+  </si>
+  <si>
+    <t>letter00094</t>
+  </si>
+  <si>
+    <t>letter00096</t>
+  </si>
+  <si>
+    <t>letter00098-A</t>
+  </si>
+  <si>
+    <t>letter00098-B</t>
+  </si>
+  <si>
+    <t>letter00100</t>
+  </si>
+  <si>
+    <t>letter00102</t>
+  </si>
+  <si>
+    <t>letter00104</t>
+  </si>
+  <si>
+    <t>letter00106</t>
+  </si>
+  <si>
+    <t>letter00108</t>
+  </si>
+  <si>
+    <t>letter00112</t>
+  </si>
+  <si>
+    <t>letter00114</t>
+  </si>
+  <si>
+    <t>letter00116</t>
+  </si>
+  <si>
+    <t>letter00118</t>
+  </si>
+  <si>
+    <t>letter00120</t>
+  </si>
+  <si>
+    <t>letter00124</t>
+  </si>
+  <si>
+    <t>letter00126</t>
+  </si>
+  <si>
+    <t>letter00128</t>
+  </si>
+  <si>
+    <t>letter00130</t>
+  </si>
+  <si>
+    <t>letter00132</t>
+  </si>
+  <si>
+    <t>letter00134</t>
+  </si>
+  <si>
+    <t>letter00136</t>
+  </si>
+  <si>
+    <t>letter00138</t>
+  </si>
+  <si>
+    <t>letter00140</t>
+  </si>
+  <si>
+    <t>letter00142</t>
+  </si>
+  <si>
+    <t>letter00144</t>
+  </si>
+  <si>
+    <t>letter00146</t>
+  </si>
+  <si>
+    <t>letter00148</t>
+  </si>
+  <si>
+    <t>letter00150</t>
+  </si>
+  <si>
+    <t>letter00152</t>
+  </si>
+  <si>
+    <t>letter00154</t>
+  </si>
+  <si>
+    <t>letter00156</t>
+  </si>
+  <si>
+    <t>letter00158</t>
+  </si>
+  <si>
+    <t>letter00160</t>
+  </si>
+  <si>
+    <t>letter00162</t>
+  </si>
+  <si>
+    <t>letter00164</t>
+  </si>
+  <si>
+    <t>letter00166</t>
+  </si>
+  <si>
+    <t>letter00168</t>
+  </si>
+  <si>
+    <t>letter00170</t>
+  </si>
+  <si>
+    <t>letter00172</t>
+  </si>
+  <si>
+    <t>letter00174</t>
+  </si>
+  <si>
+    <t>letter00176</t>
+  </si>
+  <si>
+    <t>letter00178</t>
+  </si>
+  <si>
+    <t>letter00182</t>
+  </si>
+  <si>
+    <t>letter00184</t>
+  </si>
+  <si>
+    <t>letter00186</t>
+  </si>
+  <si>
+    <t>letter00188</t>
+  </si>
+  <si>
+    <t>letter00190</t>
+  </si>
+  <si>
+    <t>letter00192</t>
+  </si>
+  <si>
+    <t>letter00194</t>
+  </si>
+  <si>
+    <t>letter00196</t>
+  </si>
+  <si>
+    <t>letter00198</t>
+  </si>
+  <si>
+    <t>letter00200</t>
+  </si>
+  <si>
+    <t>letter00202</t>
+  </si>
+  <si>
+    <t>letter00206</t>
+  </si>
+  <si>
+    <t>letter00208</t>
+  </si>
+  <si>
+    <t>letter00209</t>
+  </si>
+  <si>
+    <t>letter00210</t>
+  </si>
+  <si>
+    <t>letter00211</t>
+  </si>
+  <si>
+    <t>letter00212</t>
+  </si>
+  <si>
+    <t>letter00213</t>
+  </si>
+  <si>
+    <t>letter00214</t>
+  </si>
+  <si>
+    <t>letter00215</t>
+  </si>
+  <si>
+    <t>letter00216</t>
+  </si>
+  <si>
+    <t>letter00217</t>
+  </si>
+  <si>
+    <t>letter00218</t>
+  </si>
+  <si>
+    <t>letter00219</t>
+  </si>
+  <si>
+    <t>letter00220</t>
+  </si>
+  <si>
+    <t>letter00221</t>
+  </si>
+  <si>
+    <t>letter00222</t>
+  </si>
+  <si>
+    <t>letter00223</t>
+  </si>
+  <si>
+    <t>letter00224</t>
+  </si>
+  <si>
+    <t>letter00225</t>
+  </si>
+  <si>
+    <t>letter00226</t>
+  </si>
+  <si>
+    <t>letter00227</t>
+  </si>
+  <si>
+    <t>letter00228</t>
+  </si>
+  <si>
+    <t>letter00229</t>
+  </si>
+  <si>
+    <t>letter00230</t>
+  </si>
+  <si>
+    <t>letter00231</t>
+  </si>
+  <si>
+    <t>letter00232</t>
+  </si>
+  <si>
+    <t>letter00233</t>
+  </si>
+  <si>
+    <t>letter00234</t>
+  </si>
+  <si>
+    <t>letter00235</t>
+  </si>
+  <si>
+    <t>letter00236</t>
+  </si>
+  <si>
+    <t>letter00237</t>
+  </si>
+  <si>
+    <t>letter00238</t>
+  </si>
+  <si>
+    <t>letter00239</t>
+  </si>
+  <si>
+    <t>letter00240</t>
+  </si>
+  <si>
+    <t>letter00241</t>
+  </si>
+  <si>
+    <t>letter00242</t>
+  </si>
+  <si>
+    <t>letter00243</t>
+  </si>
+  <si>
+    <t>letter00244</t>
+  </si>
+  <si>
+    <t>letter00245</t>
+  </si>
+  <si>
+    <t>letter00246</t>
+  </si>
+  <si>
+    <t>letter00247</t>
+  </si>
+  <si>
+    <t>letter00248</t>
+  </si>
+  <si>
+    <t>letter00249</t>
+  </si>
+  <si>
+    <t>letter00250</t>
+  </si>
+  <si>
+    <t>letter00251</t>
+  </si>
+  <si>
+    <t>letter00252</t>
+  </si>
+  <si>
+    <t>letter00253</t>
+  </si>
+  <si>
+    <t>letter00254</t>
+  </si>
+  <si>
+    <t>letter00255</t>
+  </si>
+  <si>
+    <t>letter00256</t>
+  </si>
+  <si>
+    <t>letter00257</t>
+  </si>
+  <si>
+    <t>letter00258</t>
+  </si>
+  <si>
+    <t>letter00259</t>
+  </si>
+  <si>
+    <t>letter00260</t>
+  </si>
+  <si>
+    <t>letter00261</t>
+  </si>
+  <si>
+    <t>letter00262</t>
+  </si>
+  <si>
+    <t>letter00263</t>
+  </si>
+  <si>
+    <t>letter00264</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> letter00265</t>
+  </si>
+  <si>
+    <t>letter00266</t>
+  </si>
+  <si>
+    <t>letter00267</t>
+  </si>
+  <si>
+    <t>letter00268</t>
+  </si>
+  <si>
+    <t>letter00269</t>
+  </si>
+  <si>
+    <t>letter00270</t>
+  </si>
+  <si>
+    <t>letter00271</t>
+  </si>
+  <si>
+    <t>letter00272</t>
+  </si>
+  <si>
+    <t>letter00273</t>
+  </si>
+  <si>
+    <t>letter00274</t>
+  </si>
+  <si>
+    <t>letter00275</t>
+  </si>
+  <si>
+    <t>letter00276</t>
+  </si>
+  <si>
+    <t>letter00277</t>
+  </si>
+  <si>
+    <t>letter00278</t>
+  </si>
+  <si>
+    <t>letter00279</t>
+  </si>
+  <si>
+    <t>letter00280</t>
+  </si>
+  <si>
+    <t>letter00281</t>
+  </si>
+  <si>
+    <t>letter00282</t>
+  </si>
+  <si>
+    <t>letter00283</t>
+  </si>
+  <si>
+    <t>letter00284</t>
+  </si>
+  <si>
+    <t>letter00285</t>
+  </si>
+  <si>
+    <t>letter00286</t>
+  </si>
+  <si>
+    <t>letter00287</t>
+  </si>
+  <si>
+    <t>letter00288</t>
+  </si>
+  <si>
+    <t>letter00289</t>
+  </si>
+  <si>
+    <t>letter00290</t>
+  </si>
+  <si>
+    <t>letter00291</t>
+  </si>
+  <si>
+    <t>letter00292</t>
+  </si>
+  <si>
+    <t>letter00293</t>
+  </si>
+  <si>
+    <t>letter00294</t>
+  </si>
+  <si>
+    <t>letter00295</t>
+  </si>
+  <si>
+    <t>letter00296</t>
+  </si>
+  <si>
+    <t>letter00297</t>
+  </si>
+  <si>
+    <t>letter00298</t>
+  </si>
+  <si>
+    <t>letter00299</t>
+  </si>
+  <si>
+    <t>letter00300</t>
+  </si>
+  <si>
+    <t>letter00301</t>
+  </si>
+  <si>
+    <t>letter302</t>
+  </si>
+  <si>
+    <t>letter303</t>
+  </si>
+  <si>
+    <t>letter304</t>
+  </si>
+  <si>
+    <t>letter305</t>
+  </si>
+  <si>
+    <t>letter306</t>
+  </si>
+  <si>
+    <t>letter307</t>
+  </si>
+  <si>
+    <t>letter308</t>
+  </si>
+  <si>
+    <t>letter309</t>
+  </si>
+  <si>
+    <t>letter310</t>
+  </si>
+  <si>
+    <t>letter311</t>
+  </si>
+  <si>
+    <t>letter312</t>
+  </si>
+  <si>
+    <t>letter314</t>
+  </si>
+  <si>
+    <t>letter315</t>
+  </si>
+  <si>
+    <t>letter316</t>
+  </si>
+  <si>
+    <t>letter317</t>
+  </si>
+  <si>
+    <t>letter318</t>
+  </si>
+  <si>
+    <t>letter319</t>
+  </si>
+  <si>
+    <t>letter320</t>
+  </si>
+  <si>
+    <t>letter321</t>
+  </si>
+  <si>
+    <t>letter00322</t>
+  </si>
+  <si>
+    <t>letter323</t>
+  </si>
+  <si>
+    <t>letter324</t>
+  </si>
+  <si>
+    <t>letter325</t>
+  </si>
+  <si>
+    <t>letter327</t>
+  </si>
+  <si>
+    <t>letter328</t>
+  </si>
+  <si>
+    <t>letter329</t>
+  </si>
+  <si>
     <t>letter330</t>
   </si>
   <si>
-    <t>letter00029</t>
-  </si>
-  <si>
-    <t>letter00033</t>
-  </si>
-  <si>
-    <t>letter00035</t>
-  </si>
-  <si>
-    <t>letter00037</t>
-  </si>
-  <si>
-    <t>letter00039</t>
-  </si>
-  <si>
-    <t>letter00041</t>
-  </si>
-  <si>
-    <t>letter00043</t>
-  </si>
-  <si>
-    <t>letter00045</t>
-  </si>
-  <si>
-    <t>letter00047</t>
-  </si>
-  <si>
-    <t>letter00049</t>
-  </si>
-  <si>
-    <t>letter00051</t>
-  </si>
-  <si>
-    <t>letter00053</t>
-  </si>
-  <si>
-    <t>letter00057</t>
-  </si>
-  <si>
-    <t>letter00059</t>
-  </si>
-  <si>
-    <t>letter00065</t>
-  </si>
-  <si>
-    <t>letter00067</t>
-  </si>
-  <si>
-    <t>letter00069</t>
-  </si>
-  <si>
-    <t>letter00071</t>
-  </si>
-  <si>
-    <t>letter00073</t>
-  </si>
-  <si>
-    <t>letter00075</t>
-  </si>
-  <si>
-    <t>letter00077</t>
-  </si>
-  <si>
-    <t>letter00079</t>
-  </si>
-  <si>
-    <t>letter00080</t>
-  </si>
-  <si>
-    <t>letter00082</t>
-  </si>
-  <si>
-    <t>letter00084</t>
-  </si>
-  <si>
-    <t>letter00086</t>
-  </si>
-  <si>
-    <t>letter00088</t>
-  </si>
-  <si>
-    <t>letter00090</t>
-  </si>
-  <si>
-    <t>letter00092</t>
-  </si>
-  <si>
-    <t>letter00094</t>
-  </si>
-  <si>
-    <t>letter00096</t>
-  </si>
-  <si>
-    <t>letter00098-A</t>
-  </si>
-  <si>
-    <t>letter00098-B</t>
-  </si>
-  <si>
-    <t>letter00100</t>
-  </si>
-  <si>
-    <t>letter00102</t>
-  </si>
-  <si>
-    <t>letter00104</t>
-  </si>
-  <si>
-    <t>letter00106</t>
-  </si>
-  <si>
-    <t>letter00108</t>
-  </si>
-  <si>
-    <t>letter00112</t>
-  </si>
-  <si>
-    <t>letter00114</t>
-  </si>
-  <si>
-    <t>letter00116</t>
-  </si>
-  <si>
-    <t>letter00118</t>
-  </si>
-  <si>
-    <t>letter00120</t>
-  </si>
-  <si>
-    <t>letter00124</t>
-  </si>
-  <si>
-    <t>letter00126</t>
-  </si>
-  <si>
-    <t>letter00128</t>
-  </si>
-  <si>
-    <t>letter00130</t>
-  </si>
-  <si>
-    <t>letter00132</t>
-  </si>
-  <si>
-    <t>letter00134</t>
-  </si>
-  <si>
-    <t>letter00136</t>
-  </si>
-  <si>
-    <t>letter00138</t>
-  </si>
-  <si>
-    <t>letter00140</t>
-  </si>
-  <si>
-    <t>letter00142</t>
-  </si>
-  <si>
-    <t>letter00144</t>
-  </si>
-  <si>
-    <t>letter00146</t>
-  </si>
-  <si>
-    <t>letter00148</t>
-  </si>
-  <si>
-    <t>letter00150</t>
-  </si>
-  <si>
-    <t>letter00152</t>
-  </si>
-  <si>
-    <t>letter00154</t>
-  </si>
-  <si>
-    <t>letter00156</t>
-  </si>
-  <si>
-    <t>letter00158</t>
-  </si>
-  <si>
-    <t>letter00160</t>
-  </si>
-  <si>
-    <t>letter00162</t>
-  </si>
-  <si>
-    <t>letter00164</t>
-  </si>
-  <si>
-    <t>letter00166</t>
-  </si>
-  <si>
-    <t>letter00168</t>
-  </si>
-  <si>
-    <t>letter00170</t>
-  </si>
-  <si>
-    <t>letter00172</t>
-  </si>
-  <si>
-    <t>letter00174</t>
-  </si>
-  <si>
-    <t>letter00176</t>
-  </si>
-  <si>
-    <t>letter00178</t>
-  </si>
-  <si>
-    <t>letter00182</t>
-  </si>
-  <si>
-    <t>letter00184</t>
-  </si>
-  <si>
-    <t>letter00186</t>
-  </si>
-  <si>
-    <t>letter00188</t>
-  </si>
-  <si>
-    <t>letter00190</t>
-  </si>
-  <si>
-    <t>letter00192</t>
-  </si>
-  <si>
-    <t>letter00194</t>
-  </si>
-  <si>
-    <t>letter00196</t>
-  </si>
-  <si>
-    <t>letter00198</t>
-  </si>
-  <si>
-    <t>letter00200</t>
-  </si>
-  <si>
-    <t>letter00202</t>
-  </si>
-  <si>
-    <t>letter00206</t>
-  </si>
-  <si>
-    <t>letter00208</t>
-  </si>
-  <si>
-    <t>letter00209</t>
-  </si>
-  <si>
-    <t>letter00210</t>
-  </si>
-  <si>
-    <t>letter00211</t>
-  </si>
-  <si>
-    <t>letter00212</t>
-  </si>
-  <si>
-    <t>letter00213</t>
-  </si>
-  <si>
-    <t>letter00214</t>
-  </si>
-  <si>
-    <t>letter00215</t>
-  </si>
-  <si>
-    <t>letter00216</t>
-  </si>
-  <si>
-    <t>letter00217</t>
-  </si>
-  <si>
-    <t>letter00218</t>
-  </si>
-  <si>
-    <t>letter00219</t>
-  </si>
-  <si>
-    <t>letter00220</t>
-  </si>
-  <si>
-    <t>letter00221</t>
-  </si>
-  <si>
-    <t>letter00222</t>
-  </si>
-  <si>
-    <t>letter00223</t>
-  </si>
-  <si>
-    <t>letter00224</t>
-  </si>
-  <si>
-    <t>letter00225</t>
-  </si>
-  <si>
-    <t>letter00226</t>
-  </si>
-  <si>
-    <t>letter00227</t>
-  </si>
-  <si>
-    <t>letter00228</t>
-  </si>
-  <si>
-    <t>letter00229</t>
-  </si>
-  <si>
-    <t>letter00230</t>
-  </si>
-  <si>
-    <t>letter00231</t>
-  </si>
-  <si>
-    <t>letter00232</t>
-  </si>
-  <si>
-    <t>letter00233</t>
-  </si>
-  <si>
-    <t>letter00234</t>
-  </si>
-  <si>
-    <t>letter00235</t>
-  </si>
-  <si>
-    <t>letter00236</t>
-  </si>
-  <si>
-    <t>letter00237</t>
-  </si>
-  <si>
-    <t>letter00238</t>
-  </si>
-  <si>
-    <t>letter00239</t>
-  </si>
-  <si>
-    <t>letter00240</t>
-  </si>
-  <si>
-    <t>letter00241</t>
-  </si>
-  <si>
-    <t>letter00242</t>
-  </si>
-  <si>
-    <t>letter00243</t>
-  </si>
-  <si>
-    <t>letter00244</t>
-  </si>
-  <si>
-    <t>letter00245</t>
-  </si>
-  <si>
-    <t>letter00246</t>
-  </si>
-  <si>
-    <t>letter00247</t>
-  </si>
-  <si>
-    <t>letter00248</t>
-  </si>
-  <si>
-    <t>letter00249</t>
-  </si>
-  <si>
-    <t>letter00250</t>
-  </si>
-  <si>
-    <t>letter00251</t>
-  </si>
-  <si>
-    <t>letter00252</t>
-  </si>
-  <si>
-    <t>letter00253</t>
-  </si>
-  <si>
-    <t>letter00254</t>
-  </si>
-  <si>
-    <t>letter00255</t>
-  </si>
-  <si>
-    <t>letter00256</t>
-  </si>
-  <si>
-    <t>letter00257</t>
-  </si>
-  <si>
-    <t>letter00258</t>
-  </si>
-  <si>
-    <t>letter00259</t>
-  </si>
-  <si>
-    <t>letter00260</t>
-  </si>
-  <si>
-    <t>letter00261</t>
-  </si>
-  <si>
-    <t>letter00262</t>
-  </si>
-  <si>
-    <t>letter00263</t>
-  </si>
-  <si>
-    <t>letter00264</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> letter00265</t>
-  </si>
-  <si>
-    <t>letter00266</t>
-  </si>
-  <si>
-    <t>letter00267</t>
-  </si>
-  <si>
-    <t>letter00268</t>
-  </si>
-  <si>
-    <t>letter00269</t>
-  </si>
-  <si>
-    <t>letter00270</t>
-  </si>
-  <si>
-    <t>letter00271</t>
-  </si>
-  <si>
-    <t>letter00272</t>
-  </si>
-  <si>
-    <t>letter00273</t>
-  </si>
-  <si>
-    <t>letter00274</t>
-  </si>
-  <si>
-    <t>letter00275</t>
-  </si>
-  <si>
-    <t>letter00276</t>
-  </si>
-  <si>
-    <t>letter00277</t>
-  </si>
-  <si>
-    <t>letter00278</t>
-  </si>
-  <si>
-    <t>letter00279</t>
-  </si>
-  <si>
-    <t>letter00280</t>
-  </si>
-  <si>
-    <t>letter00281</t>
-  </si>
-  <si>
-    <t>letter00282</t>
-  </si>
-  <si>
-    <t>letter00283</t>
-  </si>
-  <si>
-    <t>letter00284</t>
-  </si>
-  <si>
-    <t>letter00285</t>
-  </si>
-  <si>
-    <t>letter00286</t>
-  </si>
-  <si>
-    <t>letter00287</t>
-  </si>
-  <si>
-    <t>letter00288</t>
-  </si>
-  <si>
-    <t>letter00289</t>
-  </si>
-  <si>
-    <t>letter00290</t>
-  </si>
-  <si>
-    <t>letter00291</t>
-  </si>
-  <si>
-    <t>letter00292</t>
-  </si>
-  <si>
-    <t>letter00293</t>
-  </si>
-  <si>
-    <t>letter00294</t>
-  </si>
-  <si>
-    <t>letter00295</t>
-  </si>
-  <si>
-    <t>letter00296</t>
-  </si>
-  <si>
-    <t>letter00297</t>
-  </si>
-  <si>
-    <t>letter00298</t>
-  </si>
-  <si>
-    <t>letter00299</t>
-  </si>
-  <si>
-    <t>letter00300</t>
-  </si>
-  <si>
-    <t>letter00301</t>
-  </si>
-  <si>
-    <t>letter302</t>
-  </si>
-  <si>
-    <t>letter303</t>
-  </si>
-  <si>
-    <t>letter304</t>
-  </si>
-  <si>
-    <t>letter305</t>
-  </si>
-  <si>
-    <t>letter306</t>
-  </si>
-  <si>
-    <t>letter307</t>
-  </si>
-  <si>
-    <t>letter308</t>
-  </si>
-  <si>
-    <t>letter309</t>
-  </si>
-  <si>
-    <t>letter310</t>
-  </si>
-  <si>
-    <t>letter311</t>
-  </si>
-  <si>
-    <t>letter312</t>
-  </si>
-  <si>
-    <t>letter314</t>
-  </si>
-  <si>
-    <t>letter315</t>
-  </si>
-  <si>
-    <t>letter316</t>
-  </si>
-  <si>
-    <t>letter317</t>
-  </si>
-  <si>
-    <t>letter318</t>
-  </si>
-  <si>
-    <t>letter319</t>
-  </si>
-  <si>
-    <t>letter320</t>
-  </si>
-  <si>
-    <t>letter321</t>
-  </si>
-  <si>
-    <t>letter00322</t>
-  </si>
-  <si>
-    <t>letter323</t>
-  </si>
-  <si>
-    <t>letter324</t>
-  </si>
-  <si>
-    <t>letter325</t>
-  </si>
-  <si>
-    <t>letter327</t>
-  </si>
-  <si>
-    <t>letter328</t>
-  </si>
-  <si>
-    <t>letter329</t>
-  </si>
-  <si>
     <t>letter331</t>
   </si>
   <si>
@@ -1678,612 +1678,612 @@
     <t xml:space="preserve"> تعميم بشأن تفعيل برامج فكرية موجهة خلال شهر رمضان 1443هـ</t>
   </si>
   <si>
+    <t>شكر لمدير جامعة الملك عبدالعزيز بشأن الاعتراف الأكاديمي لكلية الخدمات الطبية</t>
+  </si>
+  <si>
+    <t>تعميم بعدم المساس بأي شخص يفطر علنًا في رمضان احترامًا لحقوق الإنسان</t>
+  </si>
+  <si>
+    <t>رد على خبر منشور بشأن خطورة طريق الجفر شمال حائل</t>
+  </si>
+  <si>
+    <t>شكر لجمعية البر الخيرية بمركز جنم على جهودها خلال فترة الجائحة</t>
+  </si>
+  <si>
+    <t>أمر التغيير رقم (3) لمشروع تقديم خدمات فنية وتشغيلية للمنظومة الوطنية للتعاملات الإلكترونية الحكومية</t>
+  </si>
+  <si>
+    <t>خطاب شكر لرئيس بلدية محافظة الغزالة على جهود التنظيف وتحسين الخدمات</t>
+  </si>
+  <si>
+    <t>بشأن تنفيذ عدد من المسوح الإحصائية الميدانية بالتعاون مع الهيئة العامة للإحصاء</t>
+  </si>
+  <si>
+    <t>بشأن تنفيذ المسوح الإحصائية لعام 2025</t>
+  </si>
+  <si>
+    <t>إفادة بشأن زيارة وفد هيئة الحكومة الرقمية إلى الولايات المتحدة الأمريكية</t>
+  </si>
+  <si>
+    <t>اعتزام وفد من الهيئة زيارة الولايات المتحدة الأمريكية</t>
+  </si>
+  <si>
+    <t>طلب الموافقة على إنشاء مركز بحثي دولي متخصص في الحكومة الرقمية</t>
+  </si>
+  <si>
+    <t>بشأن ترشيح ضابط اتصال لمبادرة الذكاء الاصطناعي التوليدي للجميع – ICAIRE</t>
+  </si>
+  <si>
+    <t>اعتذار عن المشاركة في فعالية إطلاق دليل تجارب المدينة</t>
+  </si>
+  <si>
+    <t>بشأن ترشيح ممثل للمشاركة في الدورة السادسة لفريق الخبراء الحكومي</t>
+  </si>
+  <si>
+    <t>بشأن تفعيل أعمال البلاغ الرقمي</t>
+  </si>
+  <si>
+    <t>دعوة الهيئة لمعرض الدفاع العالمي في نسخته الثانية</t>
+  </si>
+  <si>
+    <t>تنسيق مشاركة المديرية العامة للجوازات في منتدى حوكمة الإنترنت</t>
+  </si>
+  <si>
+    <t>بشأن طلب تصوير مبنى مركز الابتكار والتقنيات الناشئة</t>
+  </si>
+  <si>
+    <t>طلب مساحة مؤقتة لمواقف سيارات</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> توصية بعقد ورشة</t>
+  </si>
+  <si>
+    <t>بشأن مشاركة السعودية الرقمية في مؤتمر جارتنر برشلونة 2023</t>
+  </si>
+  <si>
+    <t>تحديد نطاق عمل مركز تفاعل المستفيدين “آمر” وتفعيل استقبال الشكاوى الرقمية</t>
+  </si>
+  <si>
+    <t>الموافقة على اللائحة التنفيذية لنظام الأوسمة السعودية</t>
+  </si>
+  <si>
+    <t>تهنئة بالثقة الملكية</t>
+  </si>
+  <si>
+    <t>توحيد الهوية البصرية للمواقع والتطبيقات (التصميم الموحد)</t>
+  </si>
+  <si>
+    <t>مراجعة مسودة كراسة نظام مركز الوثائق والمحفوظات</t>
+  </si>
+  <si>
+    <t>بلاغ / متابعة صيانة</t>
+  </si>
+  <si>
+    <t>شكر على المساهمة في تحقيق المملكة المركز الأول في مؤشر نضج الخدمات الحكومية الإلكترونية والنقالة</t>
+  </si>
+  <si>
+    <t>مشاركة برنامج السعودية الرقمية في معرض جايتكس دبي 2023</t>
+  </si>
+  <si>
+    <t>تعميم بشأن ترشيح ممثل للتسجيل في منصة سوق البيانات</t>
+  </si>
+  <si>
+    <t>تسجيل شعار هيئة الحكومة الرقمية</t>
+  </si>
+  <si>
+    <t>خطاب شكر لمدير جمعية البر الخيرية بالأفاشيم</t>
+  </si>
+  <si>
+    <t>دعوة لزيارة جناح السعودية الرقمية ضمن مؤتمر LEAP24</t>
+  </si>
+  <si>
+    <t>دعوة لحضور حفل إطلاق “برنامج الشمولية الرقمية”</t>
+  </si>
+  <si>
+    <t>شكر لمشاركة وزارة التعليم في مؤتمر جارتنر لتقنية المعلومات</t>
+  </si>
+  <si>
+    <t>تحديث وثيقة المعايير الأساسية للتحول الرقمي</t>
+  </si>
+  <si>
+    <t>ترشيح منصة صحتي لتمثيل المملكة في جائزة القمة العالمية</t>
+  </si>
+  <si>
+    <t>دعوة للمشاركة في جناح السعودية الرقمية في منتدى دافوس 2024</t>
+  </si>
+  <si>
+    <t>دعوة لحضور ملتقى الحكومة الرقمية 2023</t>
+  </si>
+  <si>
+    <t>تحديد ضابط اتصال لمؤشر نضج التجربة الرقمية (2024)</t>
+  </si>
+  <si>
+    <t>نتائج قياس التحول الرقمي لعام 2023</t>
+  </si>
+  <si>
+    <t>اعتذار عن حضور حفل افتتاح مؤتمر الصحة الرقمية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اعتذار عن حضور حفل تخرج الدفعة الأولى من كلية الهندسة </t>
+  </si>
+  <si>
+    <t>دعوة لحضور ملتقى الحكومة الرقمية</t>
+  </si>
+  <si>
+    <t>دعوة لحضور ورشة “استشراف مستقبل الدبلوماسية في ظل التحولات الرقمية"</t>
+  </si>
+  <si>
+    <t>دعوة معالي وزير الإعلام للمشاركة في ملتقى الحكومة الرقمية</t>
+  </si>
+  <si>
+    <t>دعوة لحضور حفل تدشين مركز TECHXAGON للتحول الرقمي</t>
+  </si>
+  <si>
+    <t>دعوة من سفير دولة قطر لحضور حفل اليوم الوطني</t>
+  </si>
+  <si>
+    <t>إطلاق الدورة الثانية لمؤشر جاهزية تبني التقنيات الناشئة</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ترشيح د. [anonymized] في المسار البرلماني ضمن منتدى حوكمة الإنترنت</t>
+  </si>
+  <si>
+    <t>تقرير أداء الجهات الحكومية في مؤشر الأمم المتحدة لتطور الحكومة الإلكترونية – الربع الرابع 2023</t>
+  </si>
+  <si>
+    <t>مشاركة الهيئة في الاجتماع الحادي عشر لمديري برامج الحكومة الإلكترونية العرب</t>
+  </si>
+  <si>
+    <t>طلب تشكيل فريق من مؤسسة مسك للإشراف على مسار الشباب في منتدى حوكمة الإنترنت</t>
+  </si>
+  <si>
+    <t>تسليم خطاب شكر موجه من مدير مكتب تنمية الاتصالات إلى الاتحاد الدولي للاتصالات</t>
+  </si>
+  <si>
+    <t>مشاركة وفد هيئة الحكومة الرقمية في مؤتمر ICEGOV بالبرازيل</t>
+  </si>
+  <si>
+    <t>طلب ترشيح ممثل للمشاركة في فريق عمل استضافة منتدى حوكمة الإنترنت</t>
+  </si>
+  <si>
+    <t>طلب فتح حساب للهيئة في مركز خدمات المبتعثين</t>
+  </si>
+  <si>
+    <t>الرد على دعوة المشاركة في معرض الدفاع العالمي 2024</t>
+  </si>
+  <si>
+    <t>دعوة لحضور ملتقى الحكومة الرقمية – النسخة الثانية</t>
+  </si>
+  <si>
+    <t>تنسيق زيارة وفد لجنة القيادة لمنتدى حوكمة الإنترنت إلى المحكمة الافتراضية</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> طلب تأسيس خطوط هاتف وفاكس لمتطلبات تمرين صمود-</t>
+  </si>
+  <si>
+    <t>طلب إلغاء دائرة الإنترنت المقدمة من شركة الاتصالات السعودية STC</t>
+  </si>
+  <si>
+    <t>تطوير اتفاقية موارد البيانات والمعلومات مع شركة علم</t>
+  </si>
+  <si>
+    <t>ترشيح ممثل للمشاركة في فريق عمل تنظيم منتدى حوكمة الإنترنت 2024</t>
+  </si>
+  <si>
+    <t>الاعتذار عن حضور حفل تدشين نظام ربط الاتصالات الإدارية بجهات منظومة النقل</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> طلب تسمية ممثل للاستفادة من الخبرات السابقة في الفعاليات الأممية</t>
+  </si>
+  <si>
+    <t>تسليم دعوات دولية لحضور ملتقى الحكومة الرقمية 2023</t>
+  </si>
+  <si>
+    <t>إحالة تقرير تقييم مؤشر كفاءة وجودة المحتوى الرقمي لموقع وزارة الإعلام</t>
+  </si>
+  <si>
+    <t>إحالة ومراجعة الميثاق الأخلاقي لاستخدام الذكاء الاصطناعي بدول مجلس التعاون</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> طلب تسمية ممثل للمشاركة في لجنة التحول الرقمي الحكومي</t>
+  </si>
+  <si>
+    <t>ترشيح خبراء من وزارة الموارد البشرية لورشة عمل “مستقبل المهارات الرقمية في القطاع الحكومي"</t>
+  </si>
+  <si>
+    <t>دعوة رئيس هيئة مجتمع المعلومات بجمهورية رواندا لحضور ملتقى الحكومة الرقمية</t>
+  </si>
+  <si>
+    <t>طلب ترشيح ضابط اتصال لمؤشر كفاءة المحتوى للمواقع الإلكترونية – صندوق الاستثمارات العامة</t>
+  </si>
+  <si>
+    <t>طلب التعاون مع برنامج تجارب الحياة لتطوير رحلات الحج والعمرة</t>
+  </si>
+  <si>
+    <t>ترشيح مستشفى صحة الافتراضي لجائزة تكنولوجيا الحكومات</t>
+  </si>
+  <si>
+    <t>طلب تأكيد حجز مركز الملك عبدالعزيز الدولي للمؤتمرات</t>
+  </si>
+  <si>
+    <t>دعوة الهيئة الملكية لمدينة الرياض للمشاركة في منتدى دافوس 2024</t>
+  </si>
+  <si>
+    <t>التعاون مع هيئة المواصفات لاستشراف فرص إسناد أعمال الحكومة الرقمية بأسلوب المشاركة في الدخل</t>
+  </si>
+  <si>
+    <t>تمديد أعمال لجنة تفعيل الهيكل التنظيمي</t>
+  </si>
+  <si>
+    <t>شكر على مشاركة معرض العقيلات بجناح منطقة القصيم في مهرجان الجنادرية 27</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إشادة بجهود جمعية سقيا الماء وتقرير برنامج سقيا الحاج لعام 1443سقيا الحاج لعام 1443هـ</t>
+  </si>
+  <si>
+    <t>إنجازات جمعية سقيا الماء بمنطقة مكة المكرمة لعام 2021</t>
+  </si>
+  <si>
+    <t>تفعيل الاحتفاء باليوم العالمي للغة العربية</t>
+  </si>
+  <si>
+    <t>ترشيح خبير للمشاركة في لجنة دولية لتطوير سياسات الذكاء الاصطناعي</t>
+  </si>
+  <si>
+    <t>ترشيح ممثل لحضور منتدى التقنيات الناشئة</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ترشيح ممثل للمشاركة في اجتماع اللجنة الوطنية للحكومة الرقمية</t>
+  </si>
+  <si>
+    <t>ترشيح ممثل للمشاركة في المنتدى الخليجي للتحول الرقمي</t>
+  </si>
+  <si>
+    <t>ترشيح موظف لحضور دورة تدريبية في التحليل الرقمي</t>
+  </si>
+  <si>
+    <t>تفعيل الاحتفاء باليوم العالمي للغة العربية في المدينة المنورة</t>
+  </si>
+  <si>
+    <t>التأكد من توفير وسائل الوقاية من الحريق في المرافق الحكومية</t>
+  </si>
+  <si>
+    <t>تزويد جامعة الإمام بسلسلة يسير التعليمية لتعليم اللغة العربية للناطقين بغيرها</t>
+  </si>
+  <si>
+    <t>تنسيق إجراءات إقامة الحفل الختامي لجائزة المجمع في نسختها الثالثة</t>
+  </si>
+  <si>
+    <t>تنسيق إجراءات إقامة التصفيات النهائية لمسابقة (حرف)</t>
+  </si>
+  <si>
+    <t>المشاركة في ندوة (الإبل: إرث وفقه وعلم)</t>
+  </si>
+  <si>
+    <t>رد على مقترح توقيع مذكرة تفاهم بين جامعة الجوف ومجمع الملك سلمان العالمي للغة العربية</t>
+  </si>
+  <si>
+    <t>دعوة للمشاركة بورقة علمية في ندوة (الإبل في لغة العرب)</t>
+  </si>
+  <si>
+    <t>تسمية مدير حساب مجمع الملك سلمان العالمي للغة العربية في بوابة الجهات الحكومية التابعة لديوان المظالم</t>
+  </si>
+  <si>
+    <t>توقيع اتفاقية مستوى خدمة دوائر الاتصال مع مركز المعلومات الوطني</t>
+  </si>
+  <si>
+    <t>طلب الاستفادة من خبرة د. [anonymized] في تقديم برنامج تدريبي</t>
+  </si>
+  <si>
+    <t>المشاركة في تنظيم مؤتمر “اللغة العربية وتعزيز الهوية الوطنية السعودية"</t>
+  </si>
+  <si>
+    <t>ترشيح ممثلة المجمع للمشاركة في إعداد التقرير الوطني لتنفيذ توصية اليونسكو بشأن العلم المفتوح</t>
+  </si>
+  <si>
+    <t>شكر على إهداء مطبوعات مجلة الدراسات اللغوية</t>
+  </si>
+  <si>
+    <t>تفعيل الاحتفاء باليوم العالمي للغة العربية بالتعاون مع وزارة الرياضة</t>
+  </si>
+  <si>
+    <t>دعوة لحضور اجتماع لجنة تطوير البنية التحتية الرقمية</t>
+  </si>
+  <si>
+    <t>دعوة لحضور مؤتمر الذكاء الاصطناعي والتقنيات الناشئة</t>
+  </si>
+  <si>
+    <t>دعوة لحضور ورشة عمل بعنوان “الابتكار الرقمي ودوره في تعزيز الأداء الحكومي"</t>
+  </si>
+  <si>
+    <t>دعوة للمشاركة في اجتماع مجلس التحول الرقمي</t>
+  </si>
+  <si>
+    <t>دعوة للمشاركة في ملتقى الابتكار الرقمي</t>
+  </si>
+  <si>
+    <t>دعوة للمشاركة في منتدى الابتكار الحكومي</t>
+  </si>
+  <si>
+    <t>طلب إصدار تأشيرات لوفد الهيئة العامة للموانئ لحضور قمة الابتكار</t>
+  </si>
+  <si>
+    <t>طلب إطلاق مبادرة لتطوير الكفاءات في الاقتصاد الرقمي</t>
+  </si>
+  <si>
+    <t>طلب إنشاء وحدة إدارة المشاريع الرقمية في الوزارة</t>
+  </si>
+  <si>
+    <t>طلب إنشاء وحدة متخصصة للأمن السيبراني في الوزارة</t>
+  </si>
+  <si>
+    <t>طلب إيفاد موظفين للمشاركة في برنامج تدريبي دولي حول التحول الرقمي في التعليم</t>
+  </si>
+  <si>
+    <t>طلب إيفاد وفد للمشاركة في مؤتمر دولي للحوكمة الرقمية</t>
+  </si>
+  <si>
+    <t>طلب اعتماد برنامج التحول الرقمي للقطاع الزراعي</t>
+  </si>
+  <si>
+    <t>طلب اعتماد برنامج تطوير القادة الرقميين في الجهات الحكومية</t>
+  </si>
+  <si>
+    <t>طلب اعتماد خطة تطوير قطاع السياحة الرقمية</t>
+  </si>
+  <si>
+    <t>طلب اعتماد خطة تطوير قطاع النقل الذكي</t>
+  </si>
+  <si>
+    <t>طلب اعتماد مبادرة تطوير المهارات الرقمية</t>
+  </si>
+  <si>
+    <t>طلب اعتماد مشروع تطوير أنظمة النقل الذكي</t>
+  </si>
+  <si>
+    <t>طلب اعتماد مشروع تطوير البنية التحتية الرقمية</t>
+  </si>
+  <si>
+    <t>طلب اعتماد مشروع تطوير منصة إلكترونية لخدمات المستثمرين</t>
+  </si>
+  <si>
+    <t>طلب اعتماد مشروع تطوير منصة للتعلم الإلكتروني</t>
+  </si>
+  <si>
+    <t>طلب اعتماد مشروع تطوير نظام إلكتروني لإدارة الموارد البشرية</t>
+  </si>
+  <si>
+    <t>طلب اعتماد مشروع منصة إلكترونية لتلقي الشكاوى</t>
+  </si>
+  <si>
+    <t>طلب ترشيح للمشاركة في برنامج تدريبي دولي حول التحول الرقمي في التعليم</t>
+  </si>
+  <si>
+    <t>طلب الموافقة على إرسال وفد لحضور مؤتمر دولي حول التحول الرقمي</t>
+  </si>
+  <si>
+    <t>طلب الموافقة على إطلاق حملة وطنية للتوعية بأمن المعلومات</t>
+  </si>
+  <si>
+    <t>طلب الموافقة على إطلاق حملة وطنية للسلامة المرورية</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> طلب الموافقة على إطلاق مشروع التحول الرقمي للمدن الذكية</t>
+  </si>
+  <si>
+    <t>طلب الموافقة على إطلاق منصة إلكترونية</t>
+  </si>
+  <si>
+    <t>طلب الموافقة على إطلاق منصة لتقييم الأداء الوظيفي</t>
+  </si>
+  <si>
+    <t>طلب الموافقة على إطلاق منصة للتوظيف الذكي في الجهات الحكومية</t>
+  </si>
+  <si>
+    <t>طلب الموافقة على تدشين منصة إلكترونية لخدمات الإسكان</t>
+  </si>
+  <si>
+    <t>طلب الموافقة على تنظيم مؤتمر الذكاء الاصطناعي في الأمن السيبراني</t>
+  </si>
+  <si>
+    <t>طلب الموافقة على تنظيم ملتقى الابتكار الرقمي الحكومي</t>
+  </si>
+  <si>
+    <t>طلب الموافقة على تنظيم ندوة حول أمن البيانات</t>
+  </si>
+  <si>
+    <t>طلب الموافقة على تنفيذ مبادرة الابتكار في الخدمات الحكومية</t>
+  </si>
+  <si>
+    <t>طلب الموافقة على تنفيذ مشروع التحول الرقمي للخدمات العدلية</t>
+  </si>
+  <si>
+    <t>طلب الموافقة على توقيع اتفاقية تعاون محلية</t>
+  </si>
+  <si>
+    <t>طلب الموافقة على توقيع اتفاقية تعاون مع جهة دولية</t>
+  </si>
+  <si>
+    <t>طلب الموافقة على توقيع مذكرة تفاهم مع جهة محلية أو دولية</t>
+  </si>
+  <si>
+    <t>طلب الموافقة على مشروع تطوير البنية التحتية للطاقة النظيفة</t>
+  </si>
+  <si>
+    <t>طلب تخصيص ميزانية لتحديث أنظمة المراقبة الرقمية</t>
+  </si>
+  <si>
+    <t>طلب تخصيص ميزانية لمشروع تطوير أنظمة الأرشفة الإلكترونية</t>
+  </si>
+  <si>
+    <t>طلب ترشيح ممثل لحضور ورشة العمل الوطنية للتحول الرقمي</t>
+  </si>
+  <si>
+    <t>طلب تنظيم حملة توعوية عن الأمن السيبراني</t>
+  </si>
+  <si>
+    <t>طلب تنظيم دورة تدريبية حول الإدارة الرقمية للمشاريع الحكومية</t>
+  </si>
+  <si>
+    <t>طلب تنظيم مؤتمر وطني حول الذكاء الاصطناعي</t>
+  </si>
+  <si>
+    <t>طلب تنظيم منتدى الاستثمار في التقنيات الخضراء</t>
+  </si>
+  <si>
+    <t>طلب تنظيم منتدى وطني حول التحول الرقمي في القطاع المالي</t>
+  </si>
+  <si>
+    <t>طلب تنظيم ندوة حول الذكاء الاصطناعي في قطاع الصحة</t>
+  </si>
+  <si>
+    <t>طلب تنظيم ورشة عمل حول الابتكار في الخدمات الحكومية</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> طلب تنظيم ورشة عمل حول الابتكار في قطاع التعليم</t>
+  </si>
+  <si>
+    <t>طلب تنظيم ورشة عمل حول التحول الرقمي</t>
+  </si>
+  <si>
+    <t>طلب دعم تقني لمبادرة التحول الرقمي في الجهات الحكومية</t>
+  </si>
+  <si>
+    <t>طلب دعم فني لإطلاق برنامج ذكاء اصطناعي جديد</t>
+  </si>
+  <si>
+    <t>طلب دعم فني لإطلاق منصة إلكترونية</t>
+  </si>
+  <si>
+    <t>طلب دعم فني لإطلاق منصة إلكترونية جديدة</t>
+  </si>
+  <si>
+    <t>طلب دعم لإطلاق برنامج التدريب المهني في قطاع الطاقة</t>
+  </si>
+  <si>
+    <t>طلب دعم لإطلاق مبادرة التحول الرقمي الشامل في القطاع الحكومي</t>
+  </si>
+  <si>
+    <t>طلب دعم لإطلاق مشروع التحول الرقمي في القطاع الثقافي</t>
+  </si>
+  <si>
+    <t>طلب دعم لإنشاء مركز وطني لتحليل البيانات الصحية</t>
+  </si>
+  <si>
+    <t>طلب دعم لإنشاء منصة وطنية للابتكار الصحي</t>
+  </si>
+  <si>
+    <t>طلب دعم لتأسيس مركز وطني للابتكار التعليمي</t>
+  </si>
+  <si>
+    <t>طلب دعم لمبادرة تطوير الكوادر التقنية الوطنية</t>
+  </si>
+  <si>
+    <t>طلب دعم لمشروع تطوير تطبيقات حكومية رقمية</t>
+  </si>
+  <si>
+    <t>دعوة لزيارة معرض اللغة العربية للطفل</t>
+  </si>
+  <si>
+    <t>طلب تنظيم ورشة عمل بعنوان حماية الأنظمة الحكومية من الهجمات السيبرانية</t>
+  </si>
+  <si>
+    <t>طلب اعتماد برنامج تأهيل القيادات الرقمية</t>
+  </si>
+  <si>
+    <t>طلب الموافقة على إنشاء مركز ابتكار للذكاء الاصطناعي</t>
+  </si>
+  <si>
+    <t>طلب المشاركة في مشروع التحول الرقمي الخليجي المشترك</t>
+  </si>
+  <si>
+    <t>دعوة للمشاركة في مؤتمر الابتكار الحكومي الدولي</t>
+  </si>
+  <si>
+    <t>طلب دعم مالي لمبادرة التحول الرقمي في الجهات الخدمية</t>
+  </si>
+  <si>
+    <t>إفادة بخصوص الملفات الموضحة في البيان المرفق</t>
+  </si>
+  <si>
+    <t>إشعار بتنفيذ برنامج تدريبي حول إدارة الأدلة الرقمية</t>
+  </si>
+  <si>
+    <t>طلب إلغاء تقرير صادر عن برنامج يسر</t>
+  </si>
+  <si>
+    <t>طلب إعادة تفعيل خدمة الاستعلام عن الصكوك الفرعية</t>
+  </si>
+  <si>
+    <t>معالجة إصدار جوازات سفر بديلة للمواطنين في الخارج</t>
+  </si>
+  <si>
+    <t>الإفادة عن أوامر دفع البرامج التدريبية لموظفي وزارة الاتصالات وتقنية المعلومات</t>
+  </si>
+  <si>
+    <t>تهنئة بمناسبة صدور الموافقة السامية على تمديد تكليف معالي المحافظ</t>
+  </si>
+  <si>
+    <t>تهنئة بعيد الفطر المبارك لعام 1446هـ</t>
+  </si>
+  <si>
+    <t>دعوة لحضور حفل افتتاح مبنى الإدارة العامة لبنك التنمية الاجتماعية</t>
+  </si>
+  <si>
+    <t>دعوة حضور حفل المحتوى المحلي</t>
+  </si>
+  <si>
+    <t>ترشيح للمشاركة في مناقشة نتائج أداء الجهات الحكومية في مؤشر الأمم المتحدة لتطور الحكومة الإلكترونية</t>
+  </si>
+  <si>
+    <t>متابعة تحسين البنية التحتية الرقمية لمنطقة الهدا والشفا بمحافظة الطائف</t>
+  </si>
+  <si>
+    <t>إعادة تشكيل فريق عمل تنمية المحتوى المحلي</t>
+  </si>
+  <si>
+    <t>ترشيح ممثل لمتابعة بعض الفرص والإمكانات لمبادرة السعودية الخضراء</t>
+  </si>
+  <si>
+    <t>طلب شركة كينونة لتقنية المعلومات إلغاء تقرير برنامج التعاملات الإلكترونية “يسر</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> بشأن التهنئة بمناسبة حلول عيد الفطر المبارك </t>
+  </si>
+  <si>
+    <t>بشأن رغبة سفير مملكة تايلند لدى المملكة لقاء معالي المحافظ</t>
+  </si>
+  <si>
+    <t>بشأن خطاب الترشيح لحضور برنامج تدريبي بعنوان (إدارة الأدلة الرقمية)</t>
+  </si>
+  <si>
+    <t>بشأن طلب الاستثناء من المشاركة في دورة قياس التحول الرقمي</t>
+  </si>
+  <si>
+    <t>بشأن وجود تحديات في معالجة طلبات الجوازات الإلكترونية الجديدة</t>
+  </si>
+  <si>
+    <t>طلب تسمية ضابط اتصال للتنسيق بشأن مشروع رؤية استضافة كأس العالم (2034م) وخارطة الطريق</t>
+  </si>
+  <si>
+    <t>ملاحظات على المواقع الإلكترونية التابعة لوزارة النقل والخدمات اللوجستية</t>
+  </si>
+  <si>
+    <t>رد على تقرير مؤشر كفاءة المواقع الإلكترونية والمحتوى الرقمي للعام 2024</t>
+  </si>
+  <si>
+    <t>اعتذار عن حضور حفل جائزة المحتوى المحلي بنسخته الثالثة</t>
+  </si>
+  <si>
+    <t>طلب تمديد تكليف أمين عام منظمة التعاون الرقمي لأربع سنوات إضافية</t>
+  </si>
+  <si>
+    <t>الرد على تهنئة بمناسبة تمديد خدمة معالي المحافظ</t>
+  </si>
+  <si>
     <t xml:space="preserve">ترشيح متحدث للمشاركة في المسار البرلماني لمنتدى حوكمة الإنترنت </t>
   </si>
   <si>
-    <t>شكر لمدير جامعة الملك عبدالعزيز بشأن الاعتراف الأكاديمي لكلية الخدمات الطبية</t>
-  </si>
-  <si>
-    <t>تعميم بعدم المساس بأي شخص يفطر علنًا في رمضان احترامًا لحقوق الإنسان</t>
-  </si>
-  <si>
-    <t>رد على خبر منشور بشأن خطورة طريق الجفر شمال حائل</t>
-  </si>
-  <si>
-    <t>شكر لجمعية البر الخيرية بمركز جنم على جهودها خلال فترة الجائحة</t>
-  </si>
-  <si>
-    <t>أمر التغيير رقم (3) لمشروع تقديم خدمات فنية وتشغيلية للمنظومة الوطنية للتعاملات الإلكترونية الحكومية</t>
-  </si>
-  <si>
-    <t>خطاب شكر لرئيس بلدية محافظة الغزالة على جهود التنظيف وتحسين الخدمات</t>
-  </si>
-  <si>
-    <t>بشأن تنفيذ عدد من المسوح الإحصائية الميدانية بالتعاون مع الهيئة العامة للإحصاء</t>
-  </si>
-  <si>
-    <t>بشأن تنفيذ المسوح الإحصائية لعام 2025</t>
-  </si>
-  <si>
-    <t>إفادة بشأن زيارة وفد هيئة الحكومة الرقمية إلى الولايات المتحدة الأمريكية</t>
-  </si>
-  <si>
-    <t>اعتزام وفد من الهيئة زيارة الولايات المتحدة الأمريكية</t>
-  </si>
-  <si>
-    <t>طلب الموافقة على إنشاء مركز بحثي دولي متخصص في الحكومة الرقمية</t>
-  </si>
-  <si>
-    <t>بشأن ترشيح ضابط اتصال لمبادرة الذكاء الاصطناعي التوليدي للجميع – ICAIRE</t>
-  </si>
-  <si>
-    <t>اعتذار عن المشاركة في فعالية إطلاق دليل تجارب المدينة</t>
-  </si>
-  <si>
-    <t>بشأن ترشيح ممثل للمشاركة في الدورة السادسة لفريق الخبراء الحكومي</t>
-  </si>
-  <si>
-    <t>بشأن تفعيل أعمال البلاغ الرقمي</t>
-  </si>
-  <si>
-    <t>دعوة الهيئة لمعرض الدفاع العالمي في نسخته الثانية</t>
-  </si>
-  <si>
-    <t>تنسيق مشاركة المديرية العامة للجوازات في منتدى حوكمة الإنترنت</t>
-  </si>
-  <si>
-    <t>بشأن طلب تصوير مبنى مركز الابتكار والتقنيات الناشئة</t>
-  </si>
-  <si>
-    <t>طلب مساحة مؤقتة لمواقف سيارات</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> توصية بعقد ورشة</t>
-  </si>
-  <si>
-    <t>بشأن مشاركة السعودية الرقمية في مؤتمر جارتنر برشلونة 2023</t>
-  </si>
-  <si>
-    <t>تحديد نطاق عمل مركز تفاعل المستفيدين “آمر” وتفعيل استقبال الشكاوى الرقمية</t>
-  </si>
-  <si>
-    <t>الموافقة على اللائحة التنفيذية لنظام الأوسمة السعودية</t>
-  </si>
-  <si>
-    <t>تهنئة بالثقة الملكية</t>
-  </si>
-  <si>
-    <t>توحيد الهوية البصرية للمواقع والتطبيقات (التصميم الموحد)</t>
-  </si>
-  <si>
-    <t>مراجعة مسودة كراسة نظام مركز الوثائق والمحفوظات</t>
-  </si>
-  <si>
-    <t>بلاغ / متابعة صيانة</t>
-  </si>
-  <si>
-    <t>شكر على المساهمة في تحقيق المملكة المركز الأول في مؤشر نضج الخدمات الحكومية الإلكترونية والنقالة</t>
-  </si>
-  <si>
-    <t>مشاركة برنامج السعودية الرقمية في معرض جايتكس دبي 2023</t>
-  </si>
-  <si>
-    <t>تعميم بشأن ترشيح ممثل للتسجيل في منصة سوق البيانات</t>
-  </si>
-  <si>
-    <t>تسجيل شعار هيئة الحكومة الرقمية</t>
-  </si>
-  <si>
-    <t>خطاب شكر لمدير جمعية البر الخيرية بالأفاشيم</t>
-  </si>
-  <si>
-    <t>دعوة لزيارة جناح السعودية الرقمية ضمن مؤتمر LEAP24</t>
-  </si>
-  <si>
-    <t>دعوة لحضور حفل إطلاق “برنامج الشمولية الرقمية”</t>
-  </si>
-  <si>
-    <t>شكر لمشاركة وزارة التعليم في مؤتمر جارتنر لتقنية المعلومات</t>
-  </si>
-  <si>
-    <t>تحديث وثيقة المعايير الأساسية للتحول الرقمي</t>
-  </si>
-  <si>
-    <t>ترشيح منصة صحتي لتمثيل المملكة في جائزة القمة العالمية</t>
-  </si>
-  <si>
-    <t>دعوة للمشاركة في جناح السعودية الرقمية في منتدى دافوس 2024</t>
-  </si>
-  <si>
-    <t>دعوة لحضور ملتقى الحكومة الرقمية 2023</t>
-  </si>
-  <si>
-    <t>تحديد ضابط اتصال لمؤشر نضج التجربة الرقمية (2024)</t>
-  </si>
-  <si>
-    <t>نتائج قياس التحول الرقمي لعام 2023</t>
-  </si>
-  <si>
-    <t>اعتذار عن حضور حفل افتتاح مؤتمر الصحة الرقمية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اعتذار عن حضور حفل تخرج الدفعة الأولى من كلية الهندسة </t>
-  </si>
-  <si>
-    <t>دعوة لحضور ملتقى الحكومة الرقمية</t>
-  </si>
-  <si>
-    <t>دعوة لحضور ورشة “استشراف مستقبل الدبلوماسية في ظل التحولات الرقمية"</t>
-  </si>
-  <si>
-    <t>دعوة معالي وزير الإعلام للمشاركة في ملتقى الحكومة الرقمية</t>
-  </si>
-  <si>
-    <t>دعوة لحضور حفل تدشين مركز TECHXAGON للتحول الرقمي</t>
-  </si>
-  <si>
-    <t>دعوة من سفير دولة قطر لحضور حفل اليوم الوطني</t>
-  </si>
-  <si>
-    <t>إطلاق الدورة الثانية لمؤشر جاهزية تبني التقنيات الناشئة</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ترشيح د. [anonymized] في المسار البرلماني ضمن منتدى حوكمة الإنترنت</t>
-  </si>
-  <si>
-    <t>تقرير أداء الجهات الحكومية في مؤشر الأمم المتحدة لتطور الحكومة الإلكترونية – الربع الرابع 2023</t>
-  </si>
-  <si>
-    <t>مشاركة الهيئة في الاجتماع الحادي عشر لمديري برامج الحكومة الإلكترونية العرب</t>
-  </si>
-  <si>
-    <t>طلب تشكيل فريق من مؤسسة مسك للإشراف على مسار الشباب في منتدى حوكمة الإنترنت</t>
-  </si>
-  <si>
-    <t>تسليم خطاب شكر موجه من مدير مكتب تنمية الاتصالات إلى الاتحاد الدولي للاتصالات</t>
-  </si>
-  <si>
-    <t>مشاركة وفد هيئة الحكومة الرقمية في مؤتمر ICEGOV بالبرازيل</t>
-  </si>
-  <si>
-    <t>طلب ترشيح ممثل للمشاركة في فريق عمل استضافة منتدى حوكمة الإنترنت</t>
-  </si>
-  <si>
-    <t>طلب فتح حساب للهيئة في مركز خدمات المبتعثين</t>
-  </si>
-  <si>
-    <t>الرد على دعوة المشاركة في معرض الدفاع العالمي 2024</t>
-  </si>
-  <si>
-    <t>دعوة لحضور ملتقى الحكومة الرقمية – النسخة الثانية</t>
-  </si>
-  <si>
-    <t>تنسيق زيارة وفد لجنة القيادة لمنتدى حوكمة الإنترنت إلى المحكمة الافتراضية</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> طلب تأسيس خطوط هاتف وفاكس لمتطلبات تمرين صمود-</t>
-  </si>
-  <si>
-    <t>طلب إلغاء دائرة الإنترنت المقدمة من شركة الاتصالات السعودية STC</t>
-  </si>
-  <si>
-    <t>تطوير اتفاقية موارد البيانات والمعلومات مع شركة علم</t>
-  </si>
-  <si>
-    <t>ترشيح ممثل للمشاركة في فريق عمل تنظيم منتدى حوكمة الإنترنت 2024</t>
-  </si>
-  <si>
-    <t>الاعتذار عن حضور حفل تدشين نظام ربط الاتصالات الإدارية بجهات منظومة النقل</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> طلب تسمية ممثل للاستفادة من الخبرات السابقة في الفعاليات الأممية</t>
-  </si>
-  <si>
-    <t>تسليم دعوات دولية لحضور ملتقى الحكومة الرقمية 2023</t>
-  </si>
-  <si>
-    <t>إحالة تقرير تقييم مؤشر كفاءة وجودة المحتوى الرقمي لموقع وزارة الإعلام</t>
-  </si>
-  <si>
-    <t>إحالة ومراجعة الميثاق الأخلاقي لاستخدام الذكاء الاصطناعي بدول مجلس التعاون</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> طلب تسمية ممثل للمشاركة في لجنة التحول الرقمي الحكومي</t>
-  </si>
-  <si>
-    <t>ترشيح خبراء من وزارة الموارد البشرية لورشة عمل “مستقبل المهارات الرقمية في القطاع الحكومي"</t>
-  </si>
-  <si>
-    <t>دعوة رئيس هيئة مجتمع المعلومات بجمهورية رواندا لحضور ملتقى الحكومة الرقمية</t>
-  </si>
-  <si>
-    <t>طلب ترشيح ضابط اتصال لمؤشر كفاءة المحتوى للمواقع الإلكترونية – صندوق الاستثمارات العامة</t>
-  </si>
-  <si>
-    <t>طلب التعاون مع برنامج تجارب الحياة لتطوير رحلات الحج والعمرة</t>
-  </si>
-  <si>
-    <t>ترشيح مستشفى صحة الافتراضي لجائزة تكنولوجيا الحكومات</t>
-  </si>
-  <si>
-    <t>طلب تأكيد حجز مركز الملك عبدالعزيز الدولي للمؤتمرات</t>
-  </si>
-  <si>
-    <t>دعوة الهيئة الملكية لمدينة الرياض للمشاركة في منتدى دافوس 2024</t>
-  </si>
-  <si>
-    <t>التعاون مع هيئة المواصفات لاستشراف فرص إسناد أعمال الحكومة الرقمية بأسلوب المشاركة في الدخل</t>
-  </si>
-  <si>
-    <t>تمديد أعمال لجنة تفعيل الهيكل التنظيمي</t>
-  </si>
-  <si>
-    <t>شكر على مشاركة معرض العقيلات بجناح منطقة القصيم في مهرجان الجنادرية 27</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> إشادة بجهود جمعية سقيا الماء وتقرير برنامج سقيا الحاج لعام 1443سقيا الحاج لعام 1443هـ</t>
-  </si>
-  <si>
-    <t>إنجازات جمعية سقيا الماء بمنطقة مكة المكرمة لعام 2021</t>
-  </si>
-  <si>
-    <t>تفعيل الاحتفاء باليوم العالمي للغة العربية</t>
-  </si>
-  <si>
-    <t>ترشيح خبير للمشاركة في لجنة دولية لتطوير سياسات الذكاء الاصطناعي</t>
-  </si>
-  <si>
-    <t>ترشيح ممثل لحضور منتدى التقنيات الناشئة</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ترشيح ممثل للمشاركة في اجتماع اللجنة الوطنية للحكومة الرقمية</t>
-  </si>
-  <si>
-    <t>ترشيح ممثل للمشاركة في المنتدى الخليجي للتحول الرقمي</t>
-  </si>
-  <si>
-    <t>ترشيح موظف لحضور دورة تدريبية في التحليل الرقمي</t>
-  </si>
-  <si>
-    <t>تفعيل الاحتفاء باليوم العالمي للغة العربية في المدينة المنورة</t>
-  </si>
-  <si>
-    <t>التأكد من توفير وسائل الوقاية من الحريق في المرافق الحكومية</t>
-  </si>
-  <si>
-    <t>تزويد جامعة الإمام بسلسلة يسير التعليمية لتعليم اللغة العربية للناطقين بغيرها</t>
-  </si>
-  <si>
-    <t>تنسيق إجراءات إقامة الحفل الختامي لجائزة المجمع في نسختها الثالثة</t>
-  </si>
-  <si>
-    <t>تنسيق إجراءات إقامة التصفيات النهائية لمسابقة (حرف)</t>
-  </si>
-  <si>
-    <t>المشاركة في ندوة (الإبل: إرث وفقه وعلم)</t>
-  </si>
-  <si>
-    <t>رد على مقترح توقيع مذكرة تفاهم بين جامعة الجوف ومجمع الملك سلمان العالمي للغة العربية</t>
-  </si>
-  <si>
-    <t>دعوة للمشاركة بورقة علمية في ندوة (الإبل في لغة العرب)</t>
-  </si>
-  <si>
-    <t>تسمية مدير حساب مجمع الملك سلمان العالمي للغة العربية في بوابة الجهات الحكومية التابعة لديوان المظالم</t>
-  </si>
-  <si>
-    <t>توقيع اتفاقية مستوى خدمة دوائر الاتصال مع مركز المعلومات الوطني</t>
-  </si>
-  <si>
-    <t>طلب الاستفادة من خبرة د. [anonymized] في تقديم برنامج تدريبي</t>
-  </si>
-  <si>
-    <t>المشاركة في تنظيم مؤتمر “اللغة العربية وتعزيز الهوية الوطنية السعودية"</t>
-  </si>
-  <si>
-    <t>ترشيح ممثلة المجمع للمشاركة في إعداد التقرير الوطني لتنفيذ توصية اليونسكو بشأن العلم المفتوح</t>
-  </si>
-  <si>
-    <t>شكر على إهداء مطبوعات مجلة الدراسات اللغوية</t>
-  </si>
-  <si>
-    <t>تفعيل الاحتفاء باليوم العالمي للغة العربية بالتعاون مع وزارة الرياضة</t>
-  </si>
-  <si>
-    <t>دعوة لحضور اجتماع لجنة تطوير البنية التحتية الرقمية</t>
-  </si>
-  <si>
-    <t>دعوة لحضور مؤتمر الذكاء الاصطناعي والتقنيات الناشئة</t>
-  </si>
-  <si>
-    <t>دعوة لحضور ورشة عمل بعنوان “الابتكار الرقمي ودوره في تعزيز الأداء الحكومي"</t>
-  </si>
-  <si>
-    <t>دعوة للمشاركة في اجتماع مجلس التحول الرقمي</t>
-  </si>
-  <si>
-    <t>دعوة للمشاركة في ملتقى الابتكار الرقمي</t>
-  </si>
-  <si>
-    <t>دعوة للمشاركة في منتدى الابتكار الحكومي</t>
-  </si>
-  <si>
-    <t>طلب إصدار تأشيرات لوفد الهيئة العامة للموانئ لحضور قمة الابتكار</t>
-  </si>
-  <si>
-    <t>طلب إطلاق مبادرة لتطوير الكفاءات في الاقتصاد الرقمي</t>
-  </si>
-  <si>
-    <t>طلب إنشاء وحدة إدارة المشاريع الرقمية في الوزارة</t>
-  </si>
-  <si>
-    <t>طلب إنشاء وحدة متخصصة للأمن السيبراني في الوزارة</t>
-  </si>
-  <si>
-    <t>طلب إيفاد موظفين للمشاركة في برنامج تدريبي دولي حول التحول الرقمي في التعليم</t>
-  </si>
-  <si>
-    <t>طلب إيفاد وفد للمشاركة في مؤتمر دولي للحوكمة الرقمية</t>
-  </si>
-  <si>
-    <t>طلب اعتماد برنامج التحول الرقمي للقطاع الزراعي</t>
-  </si>
-  <si>
-    <t>طلب اعتماد برنامج تطوير القادة الرقميين في الجهات الحكومية</t>
-  </si>
-  <si>
-    <t>طلب اعتماد خطة تطوير قطاع السياحة الرقمية</t>
-  </si>
-  <si>
-    <t>طلب اعتماد خطة تطوير قطاع النقل الذكي</t>
-  </si>
-  <si>
-    <t>طلب اعتماد مبادرة تطوير المهارات الرقمية</t>
-  </si>
-  <si>
-    <t>طلب اعتماد مشروع تطوير أنظمة النقل الذكي</t>
-  </si>
-  <si>
-    <t>طلب اعتماد مشروع تطوير البنية التحتية الرقمية</t>
-  </si>
-  <si>
-    <t>طلب اعتماد مشروع تطوير منصة إلكترونية لخدمات المستثمرين</t>
-  </si>
-  <si>
-    <t>طلب اعتماد مشروع تطوير منصة للتعلم الإلكتروني</t>
-  </si>
-  <si>
-    <t>طلب اعتماد مشروع تطوير نظام إلكتروني لإدارة الموارد البشرية</t>
-  </si>
-  <si>
-    <t>طلب اعتماد مشروع منصة إلكترونية لتلقي الشكاوى</t>
-  </si>
-  <si>
-    <t>طلب ترشيح للمشاركة في برنامج تدريبي دولي حول التحول الرقمي في التعليم</t>
-  </si>
-  <si>
-    <t>طلب الموافقة على إرسال وفد لحضور مؤتمر دولي حول التحول الرقمي</t>
-  </si>
-  <si>
-    <t>طلب الموافقة على إطلاق حملة وطنية للتوعية بأمن المعلومات</t>
-  </si>
-  <si>
-    <t>طلب الموافقة على إطلاق حملة وطنية للسلامة المرورية</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> طلب الموافقة على إطلاق مشروع التحول الرقمي للمدن الذكية</t>
-  </si>
-  <si>
-    <t>طلب الموافقة على إطلاق منصة إلكترونية</t>
-  </si>
-  <si>
-    <t>طلب الموافقة على إطلاق منصة لتقييم الأداء الوظيفي</t>
-  </si>
-  <si>
-    <t>طلب الموافقة على إطلاق منصة للتوظيف الذكي في الجهات الحكومية</t>
-  </si>
-  <si>
-    <t>طلب الموافقة على تدشين منصة إلكترونية لخدمات الإسكان</t>
-  </si>
-  <si>
-    <t>طلب الموافقة على تنظيم مؤتمر الذكاء الاصطناعي في الأمن السيبراني</t>
-  </si>
-  <si>
-    <t>طلب الموافقة على تنظيم ملتقى الابتكار الرقمي الحكومي</t>
-  </si>
-  <si>
-    <t>طلب الموافقة على تنظيم ندوة حول أمن البيانات</t>
-  </si>
-  <si>
-    <t>طلب الموافقة على تنفيذ مبادرة الابتكار في الخدمات الحكومية</t>
-  </si>
-  <si>
-    <t>طلب الموافقة على تنفيذ مشروع التحول الرقمي للخدمات العدلية</t>
-  </si>
-  <si>
-    <t>طلب الموافقة على توقيع اتفاقية تعاون محلية</t>
-  </si>
-  <si>
-    <t>طلب الموافقة على توقيع اتفاقية تعاون مع جهة دولية</t>
-  </si>
-  <si>
-    <t>طلب الموافقة على توقيع مذكرة تفاهم مع جهة محلية أو دولية</t>
-  </si>
-  <si>
-    <t>طلب الموافقة على مشروع تطوير البنية التحتية للطاقة النظيفة</t>
-  </si>
-  <si>
-    <t>طلب تخصيص ميزانية لتحديث أنظمة المراقبة الرقمية</t>
-  </si>
-  <si>
-    <t>طلب تخصيص ميزانية لمشروع تطوير أنظمة الأرشفة الإلكترونية</t>
-  </si>
-  <si>
-    <t>طلب ترشيح ممثل لحضور ورشة العمل الوطنية للتحول الرقمي</t>
-  </si>
-  <si>
-    <t>طلب تنظيم حملة توعوية عن الأمن السيبراني</t>
-  </si>
-  <si>
-    <t>طلب تنظيم دورة تدريبية حول الإدارة الرقمية للمشاريع الحكومية</t>
-  </si>
-  <si>
-    <t>طلب تنظيم مؤتمر وطني حول الذكاء الاصطناعي</t>
-  </si>
-  <si>
-    <t>طلب تنظيم منتدى الاستثمار في التقنيات الخضراء</t>
-  </si>
-  <si>
-    <t>طلب تنظيم منتدى وطني حول التحول الرقمي في القطاع المالي</t>
-  </si>
-  <si>
-    <t>طلب تنظيم ندوة حول الذكاء الاصطناعي في قطاع الصحة</t>
-  </si>
-  <si>
-    <t>طلب تنظيم ورشة عمل حول الابتكار في الخدمات الحكومية</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> طلب تنظيم ورشة عمل حول الابتكار في قطاع التعليم</t>
-  </si>
-  <si>
-    <t>طلب تنظيم ورشة عمل حول التحول الرقمي</t>
-  </si>
-  <si>
-    <t>طلب دعم تقني لمبادرة التحول الرقمي في الجهات الحكومية</t>
-  </si>
-  <si>
-    <t>طلب دعم فني لإطلاق برنامج ذكاء اصطناعي جديد</t>
-  </si>
-  <si>
-    <t>طلب دعم فني لإطلاق منصة إلكترونية</t>
-  </si>
-  <si>
-    <t>طلب دعم فني لإطلاق منصة إلكترونية جديدة</t>
-  </si>
-  <si>
-    <t>طلب دعم لإطلاق برنامج التدريب المهني في قطاع الطاقة</t>
-  </si>
-  <si>
-    <t>طلب دعم لإطلاق مبادرة التحول الرقمي الشامل في القطاع الحكومي</t>
-  </si>
-  <si>
-    <t>طلب دعم لإطلاق مشروع التحول الرقمي في القطاع الثقافي</t>
-  </si>
-  <si>
-    <t>طلب دعم لإنشاء مركز وطني لتحليل البيانات الصحية</t>
-  </si>
-  <si>
-    <t>طلب دعم لإنشاء منصة وطنية للابتكار الصحي</t>
-  </si>
-  <si>
-    <t>طلب دعم لتأسيس مركز وطني للابتكار التعليمي</t>
-  </si>
-  <si>
-    <t>طلب دعم لمبادرة تطوير الكوادر التقنية الوطنية</t>
-  </si>
-  <si>
-    <t>طلب دعم لمشروع تطوير تطبيقات حكومية رقمية</t>
-  </si>
-  <si>
-    <t>دعوة لزيارة معرض اللغة العربية للطفل</t>
-  </si>
-  <si>
-    <t>طلب تنظيم ورشة عمل بعنوان حماية الأنظمة الحكومية من الهجمات السيبرانية</t>
-  </si>
-  <si>
-    <t>طلب اعتماد برنامج تأهيل القيادات الرقمية</t>
-  </si>
-  <si>
-    <t>طلب الموافقة على إنشاء مركز ابتكار للذكاء الاصطناعي</t>
-  </si>
-  <si>
-    <t>طلب المشاركة في مشروع التحول الرقمي الخليجي المشترك</t>
-  </si>
-  <si>
-    <t>دعوة للمشاركة في مؤتمر الابتكار الحكومي الدولي</t>
-  </si>
-  <si>
-    <t>طلب دعم مالي لمبادرة التحول الرقمي في الجهات الخدمية</t>
-  </si>
-  <si>
-    <t>إفادة بخصوص الملفات الموضحة في البيان المرفق</t>
-  </si>
-  <si>
-    <t>إشعار بتنفيذ برنامج تدريبي حول إدارة الأدلة الرقمية</t>
-  </si>
-  <si>
-    <t>طلب إلغاء تقرير صادر عن برنامج يسر</t>
-  </si>
-  <si>
-    <t>طلب إعادة تفعيل خدمة الاستعلام عن الصكوك الفرعية</t>
-  </si>
-  <si>
-    <t>معالجة إصدار جوازات سفر بديلة للمواطنين في الخارج</t>
-  </si>
-  <si>
-    <t>الإفادة عن أوامر دفع البرامج التدريبية لموظفي وزارة الاتصالات وتقنية المعلومات</t>
-  </si>
-  <si>
-    <t>تهنئة بمناسبة صدور الموافقة السامية على تمديد تكليف معالي المحافظ</t>
-  </si>
-  <si>
-    <t>تهنئة بعيد الفطر المبارك لعام 1446هـ</t>
-  </si>
-  <si>
-    <t>دعوة لحضور حفل افتتاح مبنى الإدارة العامة لبنك التنمية الاجتماعية</t>
-  </si>
-  <si>
-    <t>دعوة حضور حفل المحتوى المحلي</t>
-  </si>
-  <si>
-    <t>ترشيح للمشاركة في مناقشة نتائج أداء الجهات الحكومية في مؤشر الأمم المتحدة لتطور الحكومة الإلكترونية</t>
-  </si>
-  <si>
-    <t>متابعة تحسين البنية التحتية الرقمية لمنطقة الهدا والشفا بمحافظة الطائف</t>
-  </si>
-  <si>
-    <t>إعادة تشكيل فريق عمل تنمية المحتوى المحلي</t>
-  </si>
-  <si>
-    <t>ترشيح ممثل لمتابعة بعض الفرص والإمكانات لمبادرة السعودية الخضراء</t>
-  </si>
-  <si>
-    <t>طلب شركة كينونة لتقنية المعلومات إلغاء تقرير برنامج التعاملات الإلكترونية “يسر</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> بشأن التهنئة بمناسبة حلول عيد الفطر المبارك </t>
-  </si>
-  <si>
-    <t>بشأن رغبة سفير مملكة تايلند لدى المملكة لقاء معالي المحافظ</t>
-  </si>
-  <si>
-    <t>بشأن خطاب الترشيح لحضور برنامج تدريبي بعنوان (إدارة الأدلة الرقمية)</t>
-  </si>
-  <si>
-    <t>بشأن طلب الاستثناء من المشاركة في دورة قياس التحول الرقمي</t>
-  </si>
-  <si>
-    <t>بشأن وجود تحديات في معالجة طلبات الجوازات الإلكترونية الجديدة</t>
-  </si>
-  <si>
-    <t>طلب تسمية ضابط اتصال للتنسيق بشأن مشروع رؤية استضافة كأس العالم (2034م) وخارطة الطريق</t>
-  </si>
-  <si>
-    <t>ملاحظات على المواقع الإلكترونية التابعة لوزارة النقل والخدمات اللوجستية</t>
-  </si>
-  <si>
-    <t>رد على تقرير مؤشر كفاءة المواقع الإلكترونية والمحتوى الرقمي للعام 2024</t>
-  </si>
-  <si>
-    <t>اعتذار عن حضور حفل جائزة المحتوى المحلي بنسخته الثالثة</t>
-  </si>
-  <si>
-    <t>طلب تمديد تكليف أمين عام منظمة التعاون الرقمي لأربع سنوات إضافية</t>
-  </si>
-  <si>
-    <t>الرد على تهنئة بمناسبة تمديد خدمة معالي المحافظ</t>
-  </si>
-  <si>
     <t>اعتذار عن حضور حفل افتتاح مبنى الإدارة العامة للبنك وتدشين مقر “جادة (30“جادة (30”</t>
   </si>
   <si>
@@ -3127,19 +3127,19 @@
     <t>1443</t>
   </si>
   <si>
+    <t>1436</t>
+  </si>
+  <si>
+    <t>1441</t>
+  </si>
+  <si>
+    <t>1446</t>
+  </si>
+  <si>
+    <t>1435</t>
+  </si>
+  <si>
     <t>1439</t>
-  </si>
-  <si>
-    <t>1436</t>
-  </si>
-  <si>
-    <t>1441</t>
-  </si>
-  <si>
-    <t>1446</t>
-  </si>
-  <si>
-    <t>1435</t>
   </si>
   <si>
     <t xml:space="preserve">معالي وزير الاتصالات وتقنية المعلومات – حفظه الله
@@ -3301,16 +3301,6 @@
 والله يحفظكم ويرعاكم.
 والسلام عليكم ورحمة الله وبركاته.
 مدير عام فرع الوزارة بمنطقة المدينة المنورة</t>
-  </si>
-  <si>
-    <t>سعادة مدير التعليم بمحافظة عنيزة
-سلمه الله
-السلام عليكم ورحمة الله وبركاته
-باسمي واسم منسوبي ومقيمي دار الرعاية الاجتماعية بمحافظة عنيزة، يسرني أن أتقدم بجزيل الشكر والتقدير والامتنان لإدارتكم ولقسم تعليم الكبار لديكم على تفعيل الشراكة الاجتماعية من خلال تمكين أبنائنا المسنين دراسيًا، وتذليل كافة الصعوبات بتجهيز البيئة المدرسية المناسبة لهم، والتي كان لها الأثر الإيجابي خلال الفصل الدراسي الأول لعام 1439هـ، متطلعين إلى مزيد من التعاون لما يخدم هذه الفئة الغالية.
-سائلين الله أن يجعل ذلك في ميزان حسناتكم.
-وتقبلوا تحياتنا،،،
-مدير دار الرعاية الاجتماعية بمحافظة عنيزة
-[anonymized]</t>
   </si>
   <si>
     <t>معالي د. [anonymized] طيب
@@ -5970,6 +5960,16 @@
 والسلام عليكم ورحمة الله وبركاته.
 [anonymized]
 محافظ هيئة الحكومة الرقمية</t>
+  </si>
+  <si>
+    <t>سعادة مدير التعليم بمحافظة عنيزة
+سلمه الله
+السلام عليكم ورحمة الله وبركاته
+باسمي واسم منسوبي ومقيمي دار الرعاية الاجتماعية بمحافظة عنيزة، يسرني أن أتقدم بجزيل الشكر والتقدير والامتنان لإدارتكم ولقسم تعليم الكبار لديكم على تفعيل الشراكة الاجتماعية من خلال تمكين أبنائنا المسنين دراسيًا، وتذليل كافة الصعوبات بتجهيز البيئة المدرسية المناسبة لهم، والتي كان لها الأثر الإيجابي خلال الفصل الدراسي الأول لعام 1439هـ، متطلعين إلى مزيد من التعاون لما يخدم هذه الفئة الغالية.
+سائلين الله أن يجعل ذلك في ميزان حسناتكم.
+وتقبلوا تحياتنا،،،
+مدير دار الرعاية الاجتماعية بمحافظة عنيزة
+[anonymized]</t>
   </si>
   <si>
     <t>سعادة الرئيس التنفيذي لبنك التنمية الاجتماعية
@@ -9276,7 +9276,7 @@
         <v>554</v>
       </c>
       <c r="D16" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="E16" t="s">
         <v>1056</v>
@@ -9284,7 +9284,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
         <v>59</v>
@@ -9293,7 +9293,7 @@
         <v>555</v>
       </c>
       <c r="D17" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="E17" t="s">
         <v>1057</v>
@@ -9301,7 +9301,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
         <v>60</v>
@@ -9310,7 +9310,7 @@
         <v>556</v>
       </c>
       <c r="D18" t="s">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="E18" t="s">
         <v>1058</v>
@@ -9318,7 +9318,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B19" t="s">
         <v>61</v>
@@ -9335,7 +9335,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
         <v>62</v>
@@ -9344,7 +9344,7 @@
         <v>558</v>
       </c>
       <c r="D20" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="E20" t="s">
         <v>1060</v>
@@ -9352,7 +9352,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
         <v>63</v>
@@ -9361,7 +9361,7 @@
         <v>559</v>
       </c>
       <c r="D21" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="E21" t="s">
         <v>1061</v>
@@ -9369,7 +9369,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
         <v>64</v>
@@ -9389,13 +9389,13 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s">
         <v>561</v>
       </c>
       <c r="D23" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E23" t="s">
         <v>1063</v>
@@ -9403,7 +9403,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
         <v>65</v>
@@ -9412,7 +9412,7 @@
         <v>562</v>
       </c>
       <c r="D24" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="E24" t="s">
         <v>1064</v>
@@ -9420,7 +9420,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
         <v>66</v>
@@ -9437,7 +9437,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B26" t="s">
         <v>67</v>
@@ -9454,7 +9454,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B27" t="s">
         <v>68</v>
@@ -9471,7 +9471,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B28" t="s">
         <v>69</v>
@@ -9488,7 +9488,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B29" t="s">
         <v>70</v>
@@ -9497,7 +9497,7 @@
         <v>567</v>
       </c>
       <c r="D29" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="E29" t="s">
         <v>1069</v>
@@ -9514,7 +9514,7 @@
         <v>568</v>
       </c>
       <c r="D30" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="E30" t="s">
         <v>1070</v>
@@ -9522,7 +9522,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
         <v>72</v>
@@ -9531,7 +9531,7 @@
         <v>569</v>
       </c>
       <c r="D31" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="E31" t="s">
         <v>1071</v>
@@ -9539,7 +9539,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B32" t="s">
         <v>73</v>
@@ -9556,7 +9556,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B33" t="s">
         <v>74</v>
@@ -9565,7 +9565,7 @@
         <v>571</v>
       </c>
       <c r="D33" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="E33" t="s">
         <v>1073</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B34" t="s">
         <v>75</v>
@@ -9582,7 +9582,7 @@
         <v>572</v>
       </c>
       <c r="D34" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E34" t="s">
         <v>1074</v>
@@ -9590,7 +9590,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B35" t="s">
         <v>76</v>
@@ -9599,7 +9599,7 @@
         <v>573</v>
       </c>
       <c r="D35" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="E35" t="s">
         <v>1075</v>
@@ -9607,7 +9607,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B36" t="s">
         <v>77</v>
@@ -9616,7 +9616,7 @@
         <v>574</v>
       </c>
       <c r="D36" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="E36" t="s">
         <v>1076</v>
@@ -9624,7 +9624,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B37" t="s">
         <v>78</v>
@@ -9633,7 +9633,7 @@
         <v>575</v>
       </c>
       <c r="D37" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E37" t="s">
         <v>1077</v>
@@ -9641,7 +9641,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B38" t="s">
         <v>79</v>
@@ -9650,7 +9650,7 @@
         <v>576</v>
       </c>
       <c r="D38" t="s">
-        <v>1033</v>
+        <v>1040</v>
       </c>
       <c r="E38" t="s">
         <v>1078</v>
@@ -9658,7 +9658,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B39" t="s">
         <v>80</v>
@@ -9667,7 +9667,7 @@
         <v>577</v>
       </c>
       <c r="D39" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="E39" t="s">
         <v>1079</v>
@@ -9675,7 +9675,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B40" t="s">
         <v>81</v>
@@ -9684,7 +9684,7 @@
         <v>578</v>
       </c>
       <c r="D40" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E40" t="s">
         <v>1080</v>
@@ -9692,7 +9692,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B41" t="s">
         <v>82</v>
@@ -9701,7 +9701,7 @@
         <v>579</v>
       </c>
       <c r="D41" t="s">
-        <v>1040</v>
+        <v>1032</v>
       </c>
       <c r="E41" t="s">
         <v>1081</v>
@@ -9709,7 +9709,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B42" t="s">
         <v>83</v>
@@ -9718,7 +9718,7 @@
         <v>580</v>
       </c>
       <c r="D42" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="E42" t="s">
         <v>1082</v>
@@ -9726,7 +9726,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B43" t="s">
         <v>84</v>
@@ -9735,7 +9735,7 @@
         <v>581</v>
       </c>
       <c r="D43" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="E43" t="s">
         <v>1083</v>
@@ -9743,7 +9743,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B44" t="s">
         <v>85</v>
@@ -9760,7 +9760,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B45" t="s">
         <v>86</v>
@@ -9777,7 +9777,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B46" t="s">
         <v>87</v>
@@ -9786,7 +9786,7 @@
         <v>584</v>
       </c>
       <c r="D46" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="E46" t="s">
         <v>1086</v>
@@ -9794,7 +9794,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="B47" t="s">
         <v>88</v>
@@ -9803,7 +9803,7 @@
         <v>585</v>
       </c>
       <c r="D47" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="E47" t="s">
         <v>1087</v>
@@ -9811,16 +9811,16 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B48" t="s">
         <v>89</v>
       </c>
       <c r="C48" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="D48" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="E48" t="s">
         <v>1088</v>
@@ -9834,10 +9834,10 @@
         <v>90</v>
       </c>
       <c r="C49" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D49" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E49" t="s">
         <v>1089</v>
@@ -9845,16 +9845,16 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
         <v>91</v>
       </c>
       <c r="C50" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="D50" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="E50" t="s">
         <v>1090</v>
@@ -9862,7 +9862,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B51" t="s">
         <v>92</v>
@@ -9879,7 +9879,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B52" t="s">
         <v>93</v>
@@ -9896,7 +9896,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B53" t="s">
         <v>94</v>
@@ -9930,7 +9930,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B55" t="s">
         <v>96</v>
@@ -9964,7 +9964,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B57" t="s">
         <v>98</v>
@@ -9973,7 +9973,7 @@
         <v>593</v>
       </c>
       <c r="D57" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="E57" t="s">
         <v>1097</v>
@@ -9981,7 +9981,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B58" t="s">
         <v>99</v>
@@ -9990,7 +9990,7 @@
         <v>594</v>
       </c>
       <c r="D58" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E58" t="s">
         <v>1098</v>
@@ -9998,7 +9998,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="B59" t="s">
         <v>100</v>
@@ -10007,7 +10007,7 @@
         <v>595</v>
       </c>
       <c r="D59" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="E59" t="s">
         <v>1099</v>
@@ -10032,7 +10032,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B61" t="s">
         <v>102</v>
@@ -10041,7 +10041,7 @@
         <v>597</v>
       </c>
       <c r="D61" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E61" t="s">
         <v>1101</v>
@@ -10058,7 +10058,7 @@
         <v>598</v>
       </c>
       <c r="D62" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="E62" t="s">
         <v>1102</v>
@@ -10075,7 +10075,7 @@
         <v>599</v>
       </c>
       <c r="D63" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E63" t="s">
         <v>1103</v>
@@ -10092,7 +10092,7 @@
         <v>600</v>
       </c>
       <c r="D64" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E64" t="s">
         <v>1104</v>
@@ -10109,7 +10109,7 @@
         <v>601</v>
       </c>
       <c r="D65" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E65" t="s">
         <v>1105</v>
@@ -10117,7 +10117,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B66" t="s">
         <v>107</v>
@@ -10126,7 +10126,7 @@
         <v>602</v>
       </c>
       <c r="D66" t="s">
-        <v>1040</v>
+        <v>1031</v>
       </c>
       <c r="E66" t="s">
         <v>1106</v>
@@ -10134,7 +10134,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B67" t="s">
         <v>108</v>
@@ -10143,7 +10143,7 @@
         <v>603</v>
       </c>
       <c r="D67" t="s">
-        <v>1031</v>
+        <v>1039</v>
       </c>
       <c r="E67" t="s">
         <v>1107</v>
@@ -10151,7 +10151,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="B68" t="s">
         <v>109</v>
@@ -10160,7 +10160,7 @@
         <v>604</v>
       </c>
       <c r="D68" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="E68" t="s">
         <v>1108</v>
@@ -10168,7 +10168,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B69" t="s">
         <v>110</v>
@@ -10185,7 +10185,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B70" t="s">
         <v>111</v>
@@ -10202,7 +10202,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B71" t="s">
         <v>112</v>
@@ -10211,7 +10211,7 @@
         <v>607</v>
       </c>
       <c r="D71" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="E71" t="s">
         <v>1111</v>
@@ -10236,7 +10236,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B73" t="s">
         <v>114</v>
@@ -10245,7 +10245,7 @@
         <v>609</v>
       </c>
       <c r="D73" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E73" t="s">
         <v>1113</v>
@@ -10253,7 +10253,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B74" t="s">
         <v>115</v>
@@ -10270,7 +10270,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B75" t="s">
         <v>116</v>
@@ -10287,7 +10287,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B76" t="s">
         <v>117</v>
@@ -10304,7 +10304,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B77" t="s">
         <v>118</v>
@@ -10372,7 +10372,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B81" t="s">
         <v>122</v>
@@ -10389,7 +10389,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B82" t="s">
         <v>123</v>
@@ -10406,7 +10406,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B83" t="s">
         <v>124</v>
@@ -10423,7 +10423,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B84" t="s">
         <v>125</v>
@@ -10440,7 +10440,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B85" t="s">
         <v>126</v>
@@ -10449,7 +10449,7 @@
         <v>621</v>
       </c>
       <c r="D85" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="E85" t="s">
         <v>1125</v>
@@ -10457,7 +10457,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="B86" t="s">
         <v>127</v>
@@ -10466,7 +10466,7 @@
         <v>622</v>
       </c>
       <c r="D86" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E86" t="s">
         <v>1126</v>
@@ -10474,7 +10474,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B87" t="s">
         <v>128</v>
@@ -10508,7 +10508,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B89" t="s">
         <v>130</v>
@@ -10525,7 +10525,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B90" t="s">
         <v>131</v>
@@ -10542,7 +10542,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B91" t="s">
         <v>132</v>
@@ -10559,7 +10559,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B92" t="s">
         <v>133</v>
@@ -10576,7 +10576,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="B93" t="s">
         <v>134</v>
@@ -10593,7 +10593,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B94" t="s">
         <v>135</v>
@@ -10610,7 +10610,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B95" t="s">
         <v>136</v>
@@ -10627,7 +10627,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B96" t="s">
         <v>137</v>
@@ -10644,13 +10644,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B97" t="s">
         <v>138</v>
       </c>
       <c r="C97" t="s">
-        <v>633</v>
+        <v>564</v>
       </c>
       <c r="D97" t="s">
         <v>1033</v>
@@ -10661,16 +10661,16 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="B98" t="s">
         <v>139</v>
       </c>
       <c r="C98" t="s">
-        <v>565</v>
+        <v>633</v>
       </c>
       <c r="D98" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="E98" t="s">
         <v>1138</v>
@@ -10712,7 +10712,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B101" t="s">
         <v>142</v>
@@ -10721,7 +10721,7 @@
         <v>636</v>
       </c>
       <c r="D101" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="E101" t="s">
         <v>1141</v>
@@ -10729,7 +10729,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="B102" t="s">
         <v>143</v>
@@ -10738,7 +10738,7 @@
         <v>637</v>
       </c>
       <c r="D102" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E102" t="s">
         <v>1142</v>
@@ -10806,7 +10806,7 @@
         <v>641</v>
       </c>
       <c r="D106" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="E106" t="s">
         <v>1146</v>
@@ -10814,7 +10814,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B107" t="s">
         <v>148</v>
@@ -10823,7 +10823,7 @@
         <v>642</v>
       </c>
       <c r="D107" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="E107" t="s">
         <v>1147</v>
@@ -10840,7 +10840,7 @@
         <v>643</v>
       </c>
       <c r="D108" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="E108" t="s">
         <v>1148</v>
@@ -10848,7 +10848,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="B109" t="s">
         <v>150</v>
@@ -10857,7 +10857,7 @@
         <v>644</v>
       </c>
       <c r="D109" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E109" t="s">
         <v>1149</v>
@@ -10865,7 +10865,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B110" t="s">
         <v>151</v>
@@ -10874,7 +10874,7 @@
         <v>645</v>
       </c>
       <c r="D110" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E110" t="s">
         <v>1150</v>
@@ -10891,7 +10891,7 @@
         <v>646</v>
       </c>
       <c r="D111" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E111" t="s">
         <v>1151</v>
@@ -10908,7 +10908,7 @@
         <v>647</v>
       </c>
       <c r="D112" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E112" t="s">
         <v>1152</v>
@@ -10916,7 +10916,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="B113" t="s">
         <v>154</v>
@@ -10925,7 +10925,7 @@
         <v>648</v>
       </c>
       <c r="D113" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E113" t="s">
         <v>1153</v>
@@ -10933,7 +10933,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B114" t="s">
         <v>155</v>
@@ -10942,7 +10942,7 @@
         <v>649</v>
       </c>
       <c r="D114" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E114" t="s">
         <v>1154</v>
@@ -10950,7 +10950,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B115" t="s">
         <v>156</v>
@@ -10959,7 +10959,7 @@
         <v>650</v>
       </c>
       <c r="D115" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E115" t="s">
         <v>1155</v>
@@ -10967,7 +10967,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B116" t="s">
         <v>157</v>
@@ -10976,7 +10976,7 @@
         <v>651</v>
       </c>
       <c r="D116" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="E116" t="s">
         <v>1156</v>
@@ -10984,7 +10984,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B117" t="s">
         <v>158</v>
@@ -10993,7 +10993,7 @@
         <v>652</v>
       </c>
       <c r="D117" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="E117" t="s">
         <v>1157</v>
@@ -11001,7 +11001,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B118" t="s">
         <v>159</v>
@@ -11010,7 +11010,7 @@
         <v>653</v>
       </c>
       <c r="D118" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E118" t="s">
         <v>1158</v>
@@ -11018,7 +11018,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B119" t="s">
         <v>160</v>
@@ -11027,7 +11027,7 @@
         <v>654</v>
       </c>
       <c r="D119" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E119" t="s">
         <v>1159</v>
@@ -11035,7 +11035,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B120" t="s">
         <v>161</v>
@@ -11044,7 +11044,7 @@
         <v>655</v>
       </c>
       <c r="D120" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E120" t="s">
         <v>1160</v>
@@ -11052,7 +11052,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B121" t="s">
         <v>162</v>
@@ -11061,7 +11061,7 @@
         <v>656</v>
       </c>
       <c r="D121" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E121" t="s">
         <v>1161</v>
@@ -11069,7 +11069,7 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B122" t="s">
         <v>163</v>
@@ -11078,7 +11078,7 @@
         <v>657</v>
       </c>
       <c r="D122" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E122" t="s">
         <v>1162</v>
@@ -11095,7 +11095,7 @@
         <v>658</v>
       </c>
       <c r="D123" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="E123" t="s">
         <v>1163</v>
@@ -11112,7 +11112,7 @@
         <v>659</v>
       </c>
       <c r="D124" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="E124" t="s">
         <v>1164</v>
@@ -11129,7 +11129,7 @@
         <v>660</v>
       </c>
       <c r="D125" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E125" t="s">
         <v>1165</v>
@@ -11146,7 +11146,7 @@
         <v>661</v>
       </c>
       <c r="D126" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="E126" t="s">
         <v>1166</v>
@@ -11163,7 +11163,7 @@
         <v>662</v>
       </c>
       <c r="D127" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="E127" t="s">
         <v>1167</v>
@@ -11171,7 +11171,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B128" t="s">
         <v>169</v>
@@ -11180,7 +11180,7 @@
         <v>663</v>
       </c>
       <c r="D128" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="E128" t="s">
         <v>1168</v>
@@ -11197,7 +11197,7 @@
         <v>664</v>
       </c>
       <c r="D129" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="E129" t="s">
         <v>1169</v>
@@ -11214,7 +11214,7 @@
         <v>665</v>
       </c>
       <c r="D130" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E130" t="s">
         <v>1170</v>
@@ -11231,7 +11231,7 @@
         <v>666</v>
       </c>
       <c r="D131" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E131" t="s">
         <v>1171</v>
@@ -11248,7 +11248,7 @@
         <v>667</v>
       </c>
       <c r="D132" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E132" t="s">
         <v>1172</v>
@@ -11265,7 +11265,7 @@
         <v>668</v>
       </c>
       <c r="D133" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E133" t="s">
         <v>1173</v>
@@ -11282,7 +11282,7 @@
         <v>669</v>
       </c>
       <c r="D134" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E134" t="s">
         <v>1174</v>
@@ -11299,7 +11299,7 @@
         <v>670</v>
       </c>
       <c r="D135" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E135" t="s">
         <v>1175</v>
@@ -11316,7 +11316,7 @@
         <v>671</v>
       </c>
       <c r="D136" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E136" t="s">
         <v>1176</v>
@@ -11333,7 +11333,7 @@
         <v>672</v>
       </c>
       <c r="D137" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E137" t="s">
         <v>1177</v>
@@ -11350,7 +11350,7 @@
         <v>673</v>
       </c>
       <c r="D138" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E138" t="s">
         <v>1178</v>
@@ -11367,7 +11367,7 @@
         <v>674</v>
       </c>
       <c r="D139" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E139" t="s">
         <v>1179</v>
@@ -11384,7 +11384,7 @@
         <v>675</v>
       </c>
       <c r="D140" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E140" t="s">
         <v>1180</v>
@@ -11401,7 +11401,7 @@
         <v>676</v>
       </c>
       <c r="D141" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E141" t="s">
         <v>1181</v>
@@ -11418,7 +11418,7 @@
         <v>677</v>
       </c>
       <c r="D142" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E142" t="s">
         <v>1182</v>
@@ -11435,7 +11435,7 @@
         <v>678</v>
       </c>
       <c r="D143" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E143" t="s">
         <v>1183</v>
@@ -11452,7 +11452,7 @@
         <v>679</v>
       </c>
       <c r="D144" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E144" t="s">
         <v>1184</v>
@@ -11469,7 +11469,7 @@
         <v>680</v>
       </c>
       <c r="D145" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="E145" t="s">
         <v>1185</v>
@@ -11486,7 +11486,7 @@
         <v>681</v>
       </c>
       <c r="D146" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="E146" t="s">
         <v>1186</v>
@@ -11503,7 +11503,7 @@
         <v>682</v>
       </c>
       <c r="D147" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E147" t="s">
         <v>1187</v>
@@ -11520,7 +11520,7 @@
         <v>683</v>
       </c>
       <c r="D148" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E148" t="s">
         <v>1188</v>
@@ -11537,7 +11537,7 @@
         <v>684</v>
       </c>
       <c r="D149" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E149" t="s">
         <v>1189</v>
@@ -11554,7 +11554,7 @@
         <v>685</v>
       </c>
       <c r="D150" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E150" t="s">
         <v>1190</v>
@@ -11571,7 +11571,7 @@
         <v>686</v>
       </c>
       <c r="D151" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E151" t="s">
         <v>1191</v>
@@ -11588,7 +11588,7 @@
         <v>687</v>
       </c>
       <c r="D152" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E152" t="s">
         <v>1192</v>
@@ -11605,7 +11605,7 @@
         <v>688</v>
       </c>
       <c r="D153" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E153" t="s">
         <v>1193</v>
@@ -11622,7 +11622,7 @@
         <v>689</v>
       </c>
       <c r="D154" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E154" t="s">
         <v>1194</v>
@@ -11639,7 +11639,7 @@
         <v>690</v>
       </c>
       <c r="D155" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E155" t="s">
         <v>1195</v>
@@ -11656,7 +11656,7 @@
         <v>691</v>
       </c>
       <c r="D156" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="E156" t="s">
         <v>1196</v>
@@ -11673,7 +11673,7 @@
         <v>692</v>
       </c>
       <c r="D157" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="E157" t="s">
         <v>1197</v>
@@ -11690,7 +11690,7 @@
         <v>693</v>
       </c>
       <c r="D158" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E158" t="s">
         <v>1198</v>
@@ -11707,7 +11707,7 @@
         <v>694</v>
       </c>
       <c r="D159" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E159" t="s">
         <v>1199</v>
@@ -11724,7 +11724,7 @@
         <v>695</v>
       </c>
       <c r="D160" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E160" t="s">
         <v>1200</v>
@@ -11741,7 +11741,7 @@
         <v>696</v>
       </c>
       <c r="D161" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E161" t="s">
         <v>1201</v>
@@ -11758,7 +11758,7 @@
         <v>697</v>
       </c>
       <c r="D162" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E162" t="s">
         <v>1202</v>
@@ -11775,7 +11775,7 @@
         <v>698</v>
       </c>
       <c r="D163" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E163" t="s">
         <v>1203</v>
@@ -11792,7 +11792,7 @@
         <v>699</v>
       </c>
       <c r="D164" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E164" t="s">
         <v>1204</v>
@@ -11809,7 +11809,7 @@
         <v>700</v>
       </c>
       <c r="D165" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="E165" t="s">
         <v>1205</v>
@@ -11826,7 +11826,7 @@
         <v>701</v>
       </c>
       <c r="D166" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="E166" t="s">
         <v>1206</v>
@@ -11843,7 +11843,7 @@
         <v>702</v>
       </c>
       <c r="D167" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E167" t="s">
         <v>1207</v>
@@ -11860,7 +11860,7 @@
         <v>703</v>
       </c>
       <c r="D168" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E168" t="s">
         <v>1208</v>
@@ -11877,7 +11877,7 @@
         <v>704</v>
       </c>
       <c r="D169" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E169" t="s">
         <v>1209</v>
@@ -11894,7 +11894,7 @@
         <v>705</v>
       </c>
       <c r="D170" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E170" t="s">
         <v>1210</v>
@@ -11911,7 +11911,7 @@
         <v>706</v>
       </c>
       <c r="D171" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E171" t="s">
         <v>1211</v>
@@ -11928,7 +11928,7 @@
         <v>707</v>
       </c>
       <c r="D172" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E172" t="s">
         <v>1212</v>
@@ -11945,7 +11945,7 @@
         <v>708</v>
       </c>
       <c r="D173" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E173" t="s">
         <v>1213</v>
@@ -11962,7 +11962,7 @@
         <v>709</v>
       </c>
       <c r="D174" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E174" t="s">
         <v>1214</v>
@@ -11979,7 +11979,7 @@
         <v>710</v>
       </c>
       <c r="D175" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E175" t="s">
         <v>1215</v>
@@ -11996,7 +11996,7 @@
         <v>711</v>
       </c>
       <c r="D176" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E176" t="s">
         <v>1216</v>
@@ -12013,7 +12013,7 @@
         <v>712</v>
       </c>
       <c r="D177" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E177" t="s">
         <v>1217</v>
@@ -12030,7 +12030,7 @@
         <v>713</v>
       </c>
       <c r="D178" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E178" t="s">
         <v>1218</v>
@@ -12047,7 +12047,7 @@
         <v>714</v>
       </c>
       <c r="D179" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E179" t="s">
         <v>1219</v>
@@ -12064,7 +12064,7 @@
         <v>715</v>
       </c>
       <c r="D180" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E180" t="s">
         <v>1220</v>
@@ -12081,7 +12081,7 @@
         <v>716</v>
       </c>
       <c r="D181" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E181" t="s">
         <v>1221</v>
@@ -12098,7 +12098,7 @@
         <v>717</v>
       </c>
       <c r="D182" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E182" t="s">
         <v>1222</v>
@@ -12115,7 +12115,7 @@
         <v>718</v>
       </c>
       <c r="D183" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E183" t="s">
         <v>1223</v>
@@ -12132,7 +12132,7 @@
         <v>719</v>
       </c>
       <c r="D184" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E184" t="s">
         <v>1224</v>
@@ -12149,7 +12149,7 @@
         <v>720</v>
       </c>
       <c r="D185" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E185" t="s">
         <v>1225</v>
@@ -12166,7 +12166,7 @@
         <v>721</v>
       </c>
       <c r="D186" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E186" t="s">
         <v>1226</v>
@@ -12174,7 +12174,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B187" t="s">
         <v>228</v>
@@ -12183,7 +12183,7 @@
         <v>722</v>
       </c>
       <c r="D187" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E187" t="s">
         <v>1227</v>
@@ -12191,7 +12191,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B188" t="s">
         <v>229</v>
@@ -12200,7 +12200,7 @@
         <v>723</v>
       </c>
       <c r="D188" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E188" t="s">
         <v>1228</v>
@@ -12217,7 +12217,7 @@
         <v>724</v>
       </c>
       <c r="D189" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E189" t="s">
         <v>1229</v>
@@ -12234,7 +12234,7 @@
         <v>725</v>
       </c>
       <c r="D190" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E190" t="s">
         <v>1230</v>
@@ -12251,7 +12251,7 @@
         <v>726</v>
       </c>
       <c r="D191" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E191" t="s">
         <v>1231</v>
@@ -12259,7 +12259,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B192" t="s">
         <v>233</v>
@@ -12268,7 +12268,7 @@
         <v>727</v>
       </c>
       <c r="D192" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E192" t="s">
         <v>1232</v>
@@ -12276,7 +12276,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B193" t="s">
         <v>234</v>
@@ -12285,7 +12285,7 @@
         <v>728</v>
       </c>
       <c r="D193" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E193" t="s">
         <v>1233</v>
@@ -12293,7 +12293,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B194" t="s">
         <v>235</v>
@@ -12302,7 +12302,7 @@
         <v>729</v>
       </c>
       <c r="D194" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="E194" t="s">
         <v>1234</v>
@@ -12310,7 +12310,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B195" t="s">
         <v>236</v>
@@ -12327,7 +12327,7 @@
     </row>
     <row r="196" spans="1:5">
       <c r="A196" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B196" t="s">
         <v>237</v>
@@ -12336,7 +12336,7 @@
         <v>731</v>
       </c>
       <c r="D196" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E196" t="s">
         <v>1236</v>
@@ -12353,7 +12353,7 @@
         <v>732</v>
       </c>
       <c r="D197" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E197" t="s">
         <v>1237</v>
@@ -12361,7 +12361,7 @@
     </row>
     <row r="198" spans="1:5">
       <c r="A198" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B198" t="s">
         <v>239</v>
@@ -12370,7 +12370,7 @@
         <v>733</v>
       </c>
       <c r="D198" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E198" t="s">
         <v>1238</v>
@@ -12387,7 +12387,7 @@
         <v>734</v>
       </c>
       <c r="D199" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E199" t="s">
         <v>1239</v>
@@ -12395,7 +12395,7 @@
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B200" t="s">
         <v>241</v>
@@ -12404,7 +12404,7 @@
         <v>735</v>
       </c>
       <c r="D200" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E200" t="s">
         <v>1240</v>
@@ -12421,7 +12421,7 @@
         <v>736</v>
       </c>
       <c r="D201" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E201" t="s">
         <v>1241</v>
@@ -12429,7 +12429,7 @@
     </row>
     <row r="202" spans="1:5">
       <c r="A202" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B202" t="s">
         <v>243</v>
@@ -12438,7 +12438,7 @@
         <v>737</v>
       </c>
       <c r="D202" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E202" t="s">
         <v>1242</v>
@@ -12455,7 +12455,7 @@
         <v>738</v>
       </c>
       <c r="D203" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E203" t="s">
         <v>1243</v>
@@ -12463,7 +12463,7 @@
     </row>
     <row r="204" spans="1:5">
       <c r="A204" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B204" t="s">
         <v>245</v>
@@ -12472,7 +12472,7 @@
         <v>739</v>
       </c>
       <c r="D204" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E204" t="s">
         <v>1244</v>
@@ -12480,7 +12480,7 @@
     </row>
     <row r="205" spans="1:5">
       <c r="A205" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B205" t="s">
         <v>246</v>
@@ -12489,7 +12489,7 @@
         <v>740</v>
       </c>
       <c r="D205" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E205" t="s">
         <v>1245</v>
@@ -12497,7 +12497,7 @@
     </row>
     <row r="206" spans="1:5">
       <c r="A206" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="B206" t="s">
         <v>247</v>
@@ -12506,7 +12506,7 @@
         <v>741</v>
       </c>
       <c r="D206" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E206" t="s">
         <v>1246</v>
@@ -12514,7 +12514,7 @@
     </row>
     <row r="207" spans="1:5">
       <c r="A207" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B207" t="s">
         <v>248</v>
@@ -12523,7 +12523,7 @@
         <v>742</v>
       </c>
       <c r="D207" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E207" t="s">
         <v>1247</v>
@@ -12531,7 +12531,7 @@
     </row>
     <row r="208" spans="1:5">
       <c r="A208" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="B208" t="s">
         <v>249</v>
@@ -12540,7 +12540,7 @@
         <v>743</v>
       </c>
       <c r="D208" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E208" t="s">
         <v>1248</v>
@@ -12548,7 +12548,7 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="B209" t="s">
         <v>250</v>
@@ -12557,7 +12557,7 @@
         <v>744</v>
       </c>
       <c r="D209" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E209" t="s">
         <v>1249</v>
@@ -12574,7 +12574,7 @@
         <v>745</v>
       </c>
       <c r="D210" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E210" t="s">
         <v>1250</v>
@@ -12582,7 +12582,7 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B211" t="s">
         <v>252</v>
@@ -12591,7 +12591,7 @@
         <v>746</v>
       </c>
       <c r="D211" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E211" t="s">
         <v>1251</v>
@@ -12599,7 +12599,7 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B212" t="s">
         <v>253</v>
@@ -12608,7 +12608,7 @@
         <v>747</v>
       </c>
       <c r="D212" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E212" t="s">
         <v>1252</v>
@@ -12616,7 +12616,7 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B213" t="s">
         <v>254</v>
@@ -12625,7 +12625,7 @@
         <v>748</v>
       </c>
       <c r="D213" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E213" t="s">
         <v>1253</v>
@@ -12633,7 +12633,7 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="B214" t="s">
         <v>255</v>
@@ -12642,7 +12642,7 @@
         <v>749</v>
       </c>
       <c r="D214" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E214" t="s">
         <v>1254</v>
@@ -12650,7 +12650,7 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B215" t="s">
         <v>256</v>
@@ -12659,7 +12659,7 @@
         <v>750</v>
       </c>
       <c r="D215" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E215" t="s">
         <v>1255</v>
@@ -12676,7 +12676,7 @@
         <v>751</v>
       </c>
       <c r="D216" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E216" t="s">
         <v>1256</v>
@@ -12684,7 +12684,7 @@
     </row>
     <row r="217" spans="1:5">
       <c r="A217" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="B217" t="s">
         <v>258</v>
@@ -12693,7 +12693,7 @@
         <v>752</v>
       </c>
       <c r="D217" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E217" t="s">
         <v>1257</v>
@@ -12701,7 +12701,7 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B218" t="s">
         <v>259</v>
@@ -12710,7 +12710,7 @@
         <v>753</v>
       </c>
       <c r="D218" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E218" t="s">
         <v>1258</v>
@@ -12718,7 +12718,7 @@
     </row>
     <row r="219" spans="1:5">
       <c r="A219" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B219" t="s">
         <v>260</v>
@@ -12727,7 +12727,7 @@
         <v>754</v>
       </c>
       <c r="D219" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E219" t="s">
         <v>1259</v>
@@ -12735,7 +12735,7 @@
     </row>
     <row r="220" spans="1:5">
       <c r="A220" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="B220" t="s">
         <v>261</v>
@@ -12744,7 +12744,7 @@
         <v>755</v>
       </c>
       <c r="D220" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="E220" t="s">
         <v>1260</v>
@@ -12755,13 +12755,13 @@
         <v>31</v>
       </c>
       <c r="B221" t="s">
-        <v>58</v>
+        <v>261</v>
       </c>
       <c r="C221" t="s">
         <v>756</v>
       </c>
       <c r="D221" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E221" t="s">
         <v>1261</v>
@@ -12778,7 +12778,7 @@
         <v>757</v>
       </c>
       <c r="D222" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E222" t="s">
         <v>1262</v>
@@ -12795,7 +12795,7 @@
         <v>758</v>
       </c>
       <c r="D223" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E223" t="s">
         <v>1263</v>
@@ -12812,7 +12812,7 @@
         <v>759</v>
       </c>
       <c r="D224" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E224" t="s">
         <v>1264</v>
@@ -12829,7 +12829,7 @@
         <v>760</v>
       </c>
       <c r="D225" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E225" t="s">
         <v>1265</v>
@@ -12846,7 +12846,7 @@
         <v>761</v>
       </c>
       <c r="D226" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E226" t="s">
         <v>1266</v>
@@ -12863,7 +12863,7 @@
         <v>762</v>
       </c>
       <c r="D227" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E227" t="s">
         <v>1267</v>
@@ -12880,7 +12880,7 @@
         <v>763</v>
       </c>
       <c r="D228" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E228" t="s">
         <v>1268</v>
@@ -12897,7 +12897,7 @@
         <v>764</v>
       </c>
       <c r="D229" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E229" t="s">
         <v>1269</v>
@@ -12914,7 +12914,7 @@
         <v>765</v>
       </c>
       <c r="D230" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E230" t="s">
         <v>1270</v>
@@ -12931,7 +12931,7 @@
         <v>766</v>
       </c>
       <c r="D231" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E231" t="s">
         <v>1271</v>
@@ -12945,10 +12945,10 @@
         <v>272</v>
       </c>
       <c r="C232" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D232" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E232" t="s">
         <v>1272</v>
@@ -12965,7 +12965,7 @@
         <v>767</v>
       </c>
       <c r="D233" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E233" t="s">
         <v>1273</v>
@@ -12982,7 +12982,7 @@
         <v>768</v>
       </c>
       <c r="D234" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E234" t="s">
         <v>1274</v>
@@ -12999,7 +12999,7 @@
         <v>769</v>
       </c>
       <c r="D235" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E235" t="s">
         <v>1275</v>
@@ -13016,7 +13016,7 @@
         <v>770</v>
       </c>
       <c r="D236" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E236" t="s">
         <v>1276</v>
@@ -13033,7 +13033,7 @@
         <v>771</v>
       </c>
       <c r="D237" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E237" t="s">
         <v>1277</v>
@@ -13050,7 +13050,7 @@
         <v>772</v>
       </c>
       <c r="D238" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E238" t="s">
         <v>1278</v>
@@ -13067,7 +13067,7 @@
         <v>773</v>
       </c>
       <c r="D239" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E239" t="s">
         <v>1279</v>
@@ -13084,7 +13084,7 @@
         <v>774</v>
       </c>
       <c r="D240" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E240" t="s">
         <v>1280</v>
@@ -13101,7 +13101,7 @@
         <v>775</v>
       </c>
       <c r="D241" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E241" t="s">
         <v>1281</v>
@@ -13118,7 +13118,7 @@
         <v>776</v>
       </c>
       <c r="D242" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E242" t="s">
         <v>1282</v>
@@ -13135,7 +13135,7 @@
         <v>777</v>
       </c>
       <c r="D243" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E243" t="s">
         <v>1283</v>
@@ -13152,7 +13152,7 @@
         <v>778</v>
       </c>
       <c r="D244" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E244" t="s">
         <v>1284</v>
@@ -13169,7 +13169,7 @@
         <v>779</v>
       </c>
       <c r="D245" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E245" t="s">
         <v>1285</v>
@@ -13186,7 +13186,7 @@
         <v>780</v>
       </c>
       <c r="D246" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E246" t="s">
         <v>1286</v>
@@ -13203,7 +13203,7 @@
         <v>781</v>
       </c>
       <c r="D247" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E247" t="s">
         <v>1287</v>
@@ -13220,7 +13220,7 @@
         <v>782</v>
       </c>
       <c r="D248" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E248" t="s">
         <v>1288</v>
@@ -13237,7 +13237,7 @@
         <v>783</v>
       </c>
       <c r="D249" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E249" t="s">
         <v>1289</v>
@@ -13254,7 +13254,7 @@
         <v>784</v>
       </c>
       <c r="D250" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E250" t="s">
         <v>1290</v>
@@ -13271,7 +13271,7 @@
         <v>785</v>
       </c>
       <c r="D251" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E251" t="s">
         <v>1291</v>
@@ -13288,7 +13288,7 @@
         <v>786</v>
       </c>
       <c r="D252" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E252" t="s">
         <v>1292</v>
@@ -13305,7 +13305,7 @@
         <v>787</v>
       </c>
       <c r="D253" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E253" t="s">
         <v>1293</v>
@@ -13322,7 +13322,7 @@
         <v>788</v>
       </c>
       <c r="D254" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E254" t="s">
         <v>1294</v>
@@ -13339,7 +13339,7 @@
         <v>789</v>
       </c>
       <c r="D255" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E255" t="s">
         <v>1295</v>
@@ -13356,7 +13356,7 @@
         <v>790</v>
       </c>
       <c r="D256" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E256" t="s">
         <v>1296</v>
@@ -13373,7 +13373,7 @@
         <v>791</v>
       </c>
       <c r="D257" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E257" t="s">
         <v>1297</v>
@@ -13390,7 +13390,7 @@
         <v>792</v>
       </c>
       <c r="D258" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E258" t="s">
         <v>1298</v>
@@ -13407,7 +13407,7 @@
         <v>793</v>
       </c>
       <c r="D259" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E259" t="s">
         <v>1299</v>
@@ -13424,7 +13424,7 @@
         <v>794</v>
       </c>
       <c r="D260" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E260" t="s">
         <v>1300</v>
@@ -13441,7 +13441,7 @@
         <v>795</v>
       </c>
       <c r="D261" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E261" t="s">
         <v>1301</v>
@@ -13458,7 +13458,7 @@
         <v>796</v>
       </c>
       <c r="D262" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E262" t="s">
         <v>1302</v>
@@ -13475,7 +13475,7 @@
         <v>797</v>
       </c>
       <c r="D263" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E263" t="s">
         <v>1303</v>
@@ -13492,7 +13492,7 @@
         <v>798</v>
       </c>
       <c r="D264" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E264" t="s">
         <v>1304</v>
@@ -13509,7 +13509,7 @@
         <v>799</v>
       </c>
       <c r="D265" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E265" t="s">
         <v>1305</v>
@@ -13526,7 +13526,7 @@
         <v>800</v>
       </c>
       <c r="D266" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E266" t="s">
         <v>1306</v>
@@ -13543,7 +13543,7 @@
         <v>801</v>
       </c>
       <c r="D267" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E267" t="s">
         <v>1307</v>
@@ -13560,7 +13560,7 @@
         <v>802</v>
       </c>
       <c r="D268" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E268" t="s">
         <v>1308</v>
@@ -13577,7 +13577,7 @@
         <v>803</v>
       </c>
       <c r="D269" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E269" t="s">
         <v>1309</v>
@@ -13594,7 +13594,7 @@
         <v>804</v>
       </c>
       <c r="D270" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E270" t="s">
         <v>1310</v>
@@ -13611,7 +13611,7 @@
         <v>805</v>
       </c>
       <c r="D271" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E271" t="s">
         <v>1311</v>
@@ -13628,7 +13628,7 @@
         <v>806</v>
       </c>
       <c r="D272" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E272" t="s">
         <v>1312</v>
@@ -13645,7 +13645,7 @@
         <v>807</v>
       </c>
       <c r="D273" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E273" t="s">
         <v>1313</v>
@@ -13662,7 +13662,7 @@
         <v>808</v>
       </c>
       <c r="D274" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E274" t="s">
         <v>1314</v>
@@ -13679,7 +13679,7 @@
         <v>809</v>
       </c>
       <c r="D275" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E275" t="s">
         <v>1315</v>
@@ -13696,7 +13696,7 @@
         <v>810</v>
       </c>
       <c r="D276" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E276" t="s">
         <v>1316</v>
@@ -13713,7 +13713,7 @@
         <v>811</v>
       </c>
       <c r="D277" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E277" t="s">
         <v>1317</v>
@@ -13730,7 +13730,7 @@
         <v>812</v>
       </c>
       <c r="D278" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E278" t="s">
         <v>1318</v>
@@ -13747,7 +13747,7 @@
         <v>813</v>
       </c>
       <c r="D279" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E279" t="s">
         <v>1319</v>
@@ -13764,7 +13764,7 @@
         <v>814</v>
       </c>
       <c r="D280" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E280" t="s">
         <v>1320</v>
@@ -13781,7 +13781,7 @@
         <v>815</v>
       </c>
       <c r="D281" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E281" t="s">
         <v>1321</v>
@@ -13798,7 +13798,7 @@
         <v>816</v>
       </c>
       <c r="D282" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E282" t="s">
         <v>1322</v>
@@ -13815,7 +13815,7 @@
         <v>817</v>
       </c>
       <c r="D283" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E283" t="s">
         <v>1323</v>
@@ -13832,7 +13832,7 @@
         <v>818</v>
       </c>
       <c r="D284" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E284" t="s">
         <v>1324</v>
@@ -13849,7 +13849,7 @@
         <v>819</v>
       </c>
       <c r="D285" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E285" t="s">
         <v>1325</v>
@@ -13866,7 +13866,7 @@
         <v>820</v>
       </c>
       <c r="D286" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E286" t="s">
         <v>1326</v>
@@ -13883,7 +13883,7 @@
         <v>817</v>
       </c>
       <c r="D287" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E287" t="s">
         <v>1327</v>
@@ -13900,7 +13900,7 @@
         <v>821</v>
       </c>
       <c r="D288" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E288" t="s">
         <v>1328</v>
@@ -13917,7 +13917,7 @@
         <v>822</v>
       </c>
       <c r="D289" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E289" t="s">
         <v>1329</v>
@@ -13934,7 +13934,7 @@
         <v>823</v>
       </c>
       <c r="D290" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E290" t="s">
         <v>1330</v>
@@ -13951,7 +13951,7 @@
         <v>824</v>
       </c>
       <c r="D291" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E291" t="s">
         <v>1331</v>
@@ -13968,7 +13968,7 @@
         <v>825</v>
       </c>
       <c r="D292" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E292" t="s">
         <v>1332</v>
@@ -13985,7 +13985,7 @@
         <v>826</v>
       </c>
       <c r="D293" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E293" t="s">
         <v>1333</v>
@@ -14002,7 +14002,7 @@
         <v>827</v>
       </c>
       <c r="D294" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E294" t="s">
         <v>1334</v>
@@ -14019,7 +14019,7 @@
         <v>828</v>
       </c>
       <c r="D295" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E295" t="s">
         <v>1335</v>
@@ -14036,7 +14036,7 @@
         <v>829</v>
       </c>
       <c r="D296" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E296" t="s">
         <v>1336</v>
@@ -14053,7 +14053,7 @@
         <v>830</v>
       </c>
       <c r="D297" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E297" t="s">
         <v>1337</v>
@@ -14070,7 +14070,7 @@
         <v>831</v>
       </c>
       <c r="D298" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E298" t="s">
         <v>1338</v>
@@ -14087,7 +14087,7 @@
         <v>817</v>
       </c>
       <c r="D299" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E299" t="s">
         <v>1327</v>
@@ -14104,7 +14104,7 @@
         <v>832</v>
       </c>
       <c r="D300" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E300" t="s">
         <v>1339</v>
@@ -14121,7 +14121,7 @@
         <v>833</v>
       </c>
       <c r="D301" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E301" t="s">
         <v>1340</v>
@@ -14138,7 +14138,7 @@
         <v>834</v>
       </c>
       <c r="D302" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E302" t="s">
         <v>1341</v>
@@ -14155,7 +14155,7 @@
         <v>835</v>
       </c>
       <c r="D303" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E303" t="s">
         <v>1342</v>
@@ -14172,7 +14172,7 @@
         <v>836</v>
       </c>
       <c r="D304" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E304" t="s">
         <v>1322</v>
@@ -14189,7 +14189,7 @@
         <v>837</v>
       </c>
       <c r="D305" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E305" t="s">
         <v>1343</v>
@@ -14206,7 +14206,7 @@
         <v>838</v>
       </c>
       <c r="D306" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E306" t="s">
         <v>1344</v>
@@ -14223,7 +14223,7 @@
         <v>839</v>
       </c>
       <c r="D307" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E307" t="s">
         <v>1345</v>
@@ -14240,7 +14240,7 @@
         <v>840</v>
       </c>
       <c r="D308" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E308" t="s">
         <v>1346</v>
@@ -14257,7 +14257,7 @@
         <v>841</v>
       </c>
       <c r="D309" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E309" t="s">
         <v>1347</v>
@@ -14274,7 +14274,7 @@
         <v>842</v>
       </c>
       <c r="D310" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E310" t="s">
         <v>1348</v>
@@ -14291,7 +14291,7 @@
         <v>843</v>
       </c>
       <c r="D311" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E311" t="s">
         <v>1349</v>
@@ -14308,7 +14308,7 @@
         <v>844</v>
       </c>
       <c r="D312" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E312" t="s">
         <v>1350</v>
@@ -14325,7 +14325,7 @@
         <v>845</v>
       </c>
       <c r="D313" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E313" t="s">
         <v>1351</v>
@@ -14342,7 +14342,7 @@
         <v>846</v>
       </c>
       <c r="D314" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E314" t="s">
         <v>1352</v>
@@ -14359,7 +14359,7 @@
         <v>847</v>
       </c>
       <c r="D315" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E315" t="s">
         <v>1353</v>
@@ -14376,7 +14376,7 @@
         <v>848</v>
       </c>
       <c r="D316" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E316" t="s">
         <v>1354</v>
@@ -14393,7 +14393,7 @@
         <v>849</v>
       </c>
       <c r="D317" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E317" t="s">
         <v>1355</v>
@@ -14410,7 +14410,7 @@
         <v>850</v>
       </c>
       <c r="D318" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E318" t="s">
         <v>1356</v>
@@ -14427,7 +14427,7 @@
         <v>851</v>
       </c>
       <c r="D319" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E319" t="s">
         <v>1357</v>
@@ -14444,7 +14444,7 @@
         <v>852</v>
       </c>
       <c r="D320" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E320" t="s">
         <v>1358</v>
@@ -14461,7 +14461,7 @@
         <v>853</v>
       </c>
       <c r="D321" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E321" t="s">
         <v>1359</v>
@@ -14478,7 +14478,7 @@
         <v>854</v>
       </c>
       <c r="D322" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E322" t="s">
         <v>1360</v>
@@ -14495,7 +14495,7 @@
         <v>855</v>
       </c>
       <c r="D323" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E323" t="s">
         <v>1361</v>
@@ -14512,7 +14512,7 @@
         <v>856</v>
       </c>
       <c r="D324" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E324" t="s">
         <v>1362</v>
@@ -14529,7 +14529,7 @@
         <v>857</v>
       </c>
       <c r="D325" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E325" t="s">
         <v>1363</v>
@@ -14546,7 +14546,7 @@
         <v>858</v>
       </c>
       <c r="D326" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E326" t="s">
         <v>1364</v>
@@ -14563,7 +14563,7 @@
         <v>859</v>
       </c>
       <c r="D327" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E327" t="s">
         <v>1365</v>
@@ -14580,7 +14580,7 @@
         <v>860</v>
       </c>
       <c r="D328" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E328" t="s">
         <v>1366</v>
@@ -14597,7 +14597,7 @@
         <v>861</v>
       </c>
       <c r="D329" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E329" t="s">
         <v>1367</v>
@@ -14614,7 +14614,7 @@
         <v>862</v>
       </c>
       <c r="D330" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E330" t="s">
         <v>1368</v>
@@ -14631,7 +14631,7 @@
         <v>863</v>
       </c>
       <c r="D331" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E331" t="s">
         <v>1369</v>
@@ -14648,7 +14648,7 @@
         <v>864</v>
       </c>
       <c r="D332" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E332" t="s">
         <v>1370</v>
@@ -14665,7 +14665,7 @@
         <v>865</v>
       </c>
       <c r="D333" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E333" t="s">
         <v>1371</v>
@@ -14682,7 +14682,7 @@
         <v>866</v>
       </c>
       <c r="D334" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E334" t="s">
         <v>1372</v>
@@ -14699,7 +14699,7 @@
         <v>867</v>
       </c>
       <c r="D335" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E335" t="s">
         <v>1373</v>
@@ -14716,7 +14716,7 @@
         <v>868</v>
       </c>
       <c r="D336" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E336" t="s">
         <v>1374</v>
@@ -14733,7 +14733,7 @@
         <v>869</v>
       </c>
       <c r="D337" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E337" t="s">
         <v>1375</v>
@@ -14750,7 +14750,7 @@
         <v>870</v>
       </c>
       <c r="D338" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E338" t="s">
         <v>1376</v>
@@ -14767,7 +14767,7 @@
         <v>871</v>
       </c>
       <c r="D339" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E339" t="s">
         <v>1377</v>
@@ -14784,7 +14784,7 @@
         <v>872</v>
       </c>
       <c r="D340" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E340" t="s">
         <v>1378</v>
@@ -14801,7 +14801,7 @@
         <v>873</v>
       </c>
       <c r="D341" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E341" t="s">
         <v>1379</v>
@@ -14818,7 +14818,7 @@
         <v>874</v>
       </c>
       <c r="D342" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E342" t="s">
         <v>1380</v>
@@ -14835,7 +14835,7 @@
         <v>875</v>
       </c>
       <c r="D343" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E343" t="s">
         <v>1381</v>
@@ -14852,7 +14852,7 @@
         <v>876</v>
       </c>
       <c r="D344" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E344" t="s">
         <v>1382</v>
@@ -14869,7 +14869,7 @@
         <v>877</v>
       </c>
       <c r="D345" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E345" t="s">
         <v>1383</v>
@@ -14886,7 +14886,7 @@
         <v>878</v>
       </c>
       <c r="D346" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E346" t="s">
         <v>1384</v>
@@ -14903,7 +14903,7 @@
         <v>879</v>
       </c>
       <c r="D347" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E347" t="s">
         <v>1385</v>
@@ -14920,7 +14920,7 @@
         <v>880</v>
       </c>
       <c r="D348" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E348" t="s">
         <v>1386</v>
@@ -14937,7 +14937,7 @@
         <v>881</v>
       </c>
       <c r="D349" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E349" t="s">
         <v>1387</v>
@@ -14954,7 +14954,7 @@
         <v>882</v>
       </c>
       <c r="D350" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E350" t="s">
         <v>1388</v>
@@ -14971,7 +14971,7 @@
         <v>883</v>
       </c>
       <c r="D351" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E351" t="s">
         <v>1389</v>
@@ -14988,7 +14988,7 @@
         <v>884</v>
       </c>
       <c r="D352" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E352" t="s">
         <v>1390</v>
@@ -15005,7 +15005,7 @@
         <v>885</v>
       </c>
       <c r="D353" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E353" t="s">
         <v>1391</v>
@@ -15022,7 +15022,7 @@
         <v>886</v>
       </c>
       <c r="D354" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E354" t="s">
         <v>1392</v>
@@ -15039,7 +15039,7 @@
         <v>887</v>
       </c>
       <c r="D355" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E355" t="s">
         <v>1393</v>
@@ -15056,7 +15056,7 @@
         <v>888</v>
       </c>
       <c r="D356" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E356" t="s">
         <v>1394</v>
@@ -15073,7 +15073,7 @@
         <v>889</v>
       </c>
       <c r="D357" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E357" t="s">
         <v>1395</v>
@@ -15090,7 +15090,7 @@
         <v>890</v>
       </c>
       <c r="D358" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E358" t="s">
         <v>1396</v>
@@ -15107,7 +15107,7 @@
         <v>891</v>
       </c>
       <c r="D359" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E359" t="s">
         <v>1397</v>
@@ -15124,7 +15124,7 @@
         <v>892</v>
       </c>
       <c r="D360" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E360" t="s">
         <v>1398</v>
@@ -15141,7 +15141,7 @@
         <v>893</v>
       </c>
       <c r="D361" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E361" t="s">
         <v>1399</v>
@@ -15158,7 +15158,7 @@
         <v>894</v>
       </c>
       <c r="D362" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E362" t="s">
         <v>1400</v>
@@ -15175,7 +15175,7 @@
         <v>895</v>
       </c>
       <c r="D363" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E363" t="s">
         <v>1401</v>
@@ -15192,7 +15192,7 @@
         <v>896</v>
       </c>
       <c r="D364" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E364" t="s">
         <v>1402</v>
@@ -15209,7 +15209,7 @@
         <v>897</v>
       </c>
       <c r="D365" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E365" t="s">
         <v>1403</v>
@@ -15226,7 +15226,7 @@
         <v>898</v>
       </c>
       <c r="D366" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E366" t="s">
         <v>1404</v>
@@ -15243,7 +15243,7 @@
         <v>899</v>
       </c>
       <c r="D367" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E367" t="s">
         <v>1405</v>
@@ -15260,7 +15260,7 @@
         <v>900</v>
       </c>
       <c r="D368" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E368" t="s">
         <v>1406</v>
@@ -15277,7 +15277,7 @@
         <v>901</v>
       </c>
       <c r="D369" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E369" t="s">
         <v>1407</v>
@@ -15294,7 +15294,7 @@
         <v>902</v>
       </c>
       <c r="D370" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E370" t="s">
         <v>1408</v>
@@ -15311,7 +15311,7 @@
         <v>903</v>
       </c>
       <c r="D371" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E371" t="s">
         <v>1409</v>
@@ -15328,7 +15328,7 @@
         <v>904</v>
       </c>
       <c r="D372" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E372" t="s">
         <v>1410</v>
@@ -15345,7 +15345,7 @@
         <v>905</v>
       </c>
       <c r="D373" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E373" t="s">
         <v>1411</v>
@@ -15362,7 +15362,7 @@
         <v>906</v>
       </c>
       <c r="D374" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E374" t="s">
         <v>1409</v>
@@ -15379,7 +15379,7 @@
         <v>907</v>
       </c>
       <c r="D375" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E375" t="s">
         <v>1412</v>
@@ -15396,7 +15396,7 @@
         <v>908</v>
       </c>
       <c r="D376" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E376" t="s">
         <v>1413</v>
@@ -15413,7 +15413,7 @@
         <v>909</v>
       </c>
       <c r="D377" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E377" t="s">
         <v>1414</v>
@@ -15430,7 +15430,7 @@
         <v>910</v>
       </c>
       <c r="D378" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E378" t="s">
         <v>1415</v>
@@ -15447,7 +15447,7 @@
         <v>911</v>
       </c>
       <c r="D379" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E379" t="s">
         <v>1416</v>
@@ -15464,7 +15464,7 @@
         <v>912</v>
       </c>
       <c r="D380" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E380" t="s">
         <v>1417</v>
@@ -15481,7 +15481,7 @@
         <v>913</v>
       </c>
       <c r="D381" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E381" t="s">
         <v>1418</v>
@@ -15498,7 +15498,7 @@
         <v>914</v>
       </c>
       <c r="D382" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E382" t="s">
         <v>1419</v>
@@ -15515,7 +15515,7 @@
         <v>915</v>
       </c>
       <c r="D383" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E383" t="s">
         <v>1420</v>
@@ -15532,7 +15532,7 @@
         <v>916</v>
       </c>
       <c r="D384" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E384" t="s">
         <v>1326</v>
@@ -15549,7 +15549,7 @@
         <v>917</v>
       </c>
       <c r="D385" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E385" t="s">
         <v>1327</v>
@@ -15566,7 +15566,7 @@
         <v>918</v>
       </c>
       <c r="D386" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E386" t="s">
         <v>1421</v>
@@ -15583,7 +15583,7 @@
         <v>919</v>
       </c>
       <c r="D387" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E387" t="s">
         <v>1422</v>
@@ -15600,7 +15600,7 @@
         <v>920</v>
       </c>
       <c r="D388" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E388" t="s">
         <v>1423</v>
@@ -15617,7 +15617,7 @@
         <v>921</v>
       </c>
       <c r="D389" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E389" t="s">
         <v>1424</v>
@@ -15634,7 +15634,7 @@
         <v>922</v>
       </c>
       <c r="D390" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E390" t="s">
         <v>1425</v>
@@ -15651,7 +15651,7 @@
         <v>923</v>
       </c>
       <c r="D391" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E391" t="s">
         <v>1375</v>
@@ -15668,7 +15668,7 @@
         <v>924</v>
       </c>
       <c r="D392" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E392" t="s">
         <v>1426</v>
@@ -15685,7 +15685,7 @@
         <v>925</v>
       </c>
       <c r="D393" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E393" t="s">
         <v>1427</v>
@@ -15702,7 +15702,7 @@
         <v>926</v>
       </c>
       <c r="D394" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E394" t="s">
         <v>1428</v>
@@ -15719,7 +15719,7 @@
         <v>927</v>
       </c>
       <c r="D395" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E395" t="s">
         <v>1429</v>
@@ -15736,7 +15736,7 @@
         <v>928</v>
       </c>
       <c r="D396" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E396" t="s">
         <v>1430</v>
@@ -15753,7 +15753,7 @@
         <v>929</v>
       </c>
       <c r="D397" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E397" t="s">
         <v>1431</v>
@@ -15770,7 +15770,7 @@
         <v>930</v>
       </c>
       <c r="D398" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E398" t="s">
         <v>1432</v>
@@ -15787,7 +15787,7 @@
         <v>931</v>
       </c>
       <c r="D399" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E399" t="s">
         <v>1433</v>
@@ -15804,7 +15804,7 @@
         <v>932</v>
       </c>
       <c r="D400" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E400" t="s">
         <v>1434</v>
@@ -15821,7 +15821,7 @@
         <v>933</v>
       </c>
       <c r="D401" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E401" t="s">
         <v>1435</v>
@@ -15838,7 +15838,7 @@
         <v>934</v>
       </c>
       <c r="D402" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E402" t="s">
         <v>1436</v>
@@ -15855,7 +15855,7 @@
         <v>935</v>
       </c>
       <c r="D403" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E403" t="s">
         <v>1437</v>
@@ -15872,7 +15872,7 @@
         <v>936</v>
       </c>
       <c r="D404" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E404" t="s">
         <v>1438</v>
@@ -15889,7 +15889,7 @@
         <v>937</v>
       </c>
       <c r="D405" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E405" t="s">
         <v>1439</v>
@@ -15906,7 +15906,7 @@
         <v>938</v>
       </c>
       <c r="D406" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E406" t="s">
         <v>1440</v>
@@ -15920,7 +15920,7 @@
         <v>447</v>
       </c>
       <c r="D407" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E407" t="s">
         <v>1441</v>
@@ -15937,7 +15937,7 @@
         <v>939</v>
       </c>
       <c r="D408" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E408" t="s">
         <v>1442</v>
@@ -15954,7 +15954,7 @@
         <v>940</v>
       </c>
       <c r="D409" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E409" t="s">
         <v>1443</v>
@@ -15971,7 +15971,7 @@
         <v>941</v>
       </c>
       <c r="D410" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E410" t="s">
         <v>1444</v>
@@ -15988,7 +15988,7 @@
         <v>942</v>
       </c>
       <c r="D411" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E411" t="s">
         <v>1445</v>
@@ -16005,7 +16005,7 @@
         <v>943</v>
       </c>
       <c r="D412" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E412" t="s">
         <v>1446</v>
@@ -16022,7 +16022,7 @@
         <v>944</v>
       </c>
       <c r="D413" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E413" t="s">
         <v>1447</v>
@@ -16039,7 +16039,7 @@
         <v>945</v>
       </c>
       <c r="D414" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E414" t="s">
         <v>1448</v>
@@ -16056,7 +16056,7 @@
         <v>946</v>
       </c>
       <c r="D415" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E415" t="s">
         <v>1449</v>
@@ -16073,7 +16073,7 @@
         <v>947</v>
       </c>
       <c r="D416" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E416" t="s">
         <v>1450</v>
@@ -16090,7 +16090,7 @@
         <v>948</v>
       </c>
       <c r="D417" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E417" t="s">
         <v>1451</v>
@@ -16107,7 +16107,7 @@
         <v>949</v>
       </c>
       <c r="D418" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E418" t="s">
         <v>1452</v>
@@ -16124,7 +16124,7 @@
         <v>950</v>
       </c>
       <c r="D419" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E419" t="s">
         <v>1453</v>
@@ -16141,7 +16141,7 @@
         <v>951</v>
       </c>
       <c r="D420" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E420" t="s">
         <v>1454</v>
@@ -16158,7 +16158,7 @@
         <v>952</v>
       </c>
       <c r="D421" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E421" t="s">
         <v>1455</v>
@@ -16175,7 +16175,7 @@
         <v>953</v>
       </c>
       <c r="D422" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E422" t="s">
         <v>1456</v>
@@ -16192,7 +16192,7 @@
         <v>954</v>
       </c>
       <c r="D423" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E423" t="s">
         <v>1457</v>
@@ -16209,7 +16209,7 @@
         <v>955</v>
       </c>
       <c r="D424" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E424" t="s">
         <v>1458</v>
@@ -16226,7 +16226,7 @@
         <v>956</v>
       </c>
       <c r="D425" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E425" t="s">
         <v>1459</v>
@@ -16243,7 +16243,7 @@
         <v>957</v>
       </c>
       <c r="D426" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E426" t="s">
         <v>1460</v>
@@ -16260,7 +16260,7 @@
         <v>958</v>
       </c>
       <c r="D427" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E427" t="s">
         <v>1461</v>
@@ -16277,7 +16277,7 @@
         <v>959</v>
       </c>
       <c r="D428" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E428" t="s">
         <v>1462</v>
@@ -16294,7 +16294,7 @@
         <v>960</v>
       </c>
       <c r="D429" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E429" t="s">
         <v>1463</v>
@@ -16311,7 +16311,7 @@
         <v>961</v>
       </c>
       <c r="D430" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E430" t="s">
         <v>1464</v>
@@ -16328,7 +16328,7 @@
         <v>962</v>
       </c>
       <c r="D431" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E431" t="s">
         <v>1465</v>
